--- a/lomonosov readings 2026/explore_data/_time_series_decomposition_quarterly.xlsx
+++ b/lomonosov readings 2026/explore_data/_time_series_decomposition_quarterly.xlsx
@@ -1,46 +1,159 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>Страна</t>
+  </si>
+  <si>
+    <t>variable_country</t>
+  </si>
+  <si>
+    <t>ВВП</t>
+  </si>
+  <si>
+    <t>ВВП (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Задолженность</t>
+  </si>
+  <si>
+    <t>Задолженность (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Капитализация</t>
+  </si>
+  <si>
+    <t>Капитализация (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Объем торгов</t>
+  </si>
+  <si>
+    <t>Объем торгов (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Экспорт</t>
+  </si>
+  <si>
+    <t>Экспорт (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Индия</t>
+  </si>
+  <si>
+    <t>Китай</t>
+  </si>
+  <si>
+    <t>Индия - ВВП</t>
+  </si>
+  <si>
+    <t>Китай - ВВП</t>
+  </si>
+  <si>
+    <t>Индия - ВВП (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Китай - ВВП (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Индия - Задолженность</t>
+  </si>
+  <si>
+    <t>Китай - Задолженность</t>
+  </si>
+  <si>
+    <t>Индия - Задолженность (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Китай - Задолженность (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Индия - Капитализация</t>
+  </si>
+  <si>
+    <t>Китай - Капитализация</t>
+  </si>
+  <si>
+    <t>Индия - Капитализация (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Китай - Капитализация (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Индия - Объем торгов</t>
+  </si>
+  <si>
+    <t>Китай - Объем торгов</t>
+  </si>
+  <si>
+    <t>Китай - Объем торгов (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Индия - Экспорт</t>
+  </si>
+  <si>
+    <t>Китай - Экспорт</t>
+  </si>
+  <si>
+    <t>Индия - Экспорт (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>Китай - Экспорт (сезонность устранена) STL</t>
+  </si>
+  <si>
+    <t>report_date</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,30 +162,18 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -80,86 +181,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -447,6625 +481,6516 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:T106"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>variable</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ВВП</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>ВВП (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Задолженность</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Задолженность (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Капитализация</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="n"/>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Капитализация (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Объем торгов</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Объем торгов (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Экспорт</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Экспорт (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Страна</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t>Индия</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t>Китай</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>variable_country</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - ВВП</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - ВВП</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - ВВП (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - ВВП (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - Задолженность</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Задолженность</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - Задолженность (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Задолженность (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - Капитализация</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Капитализация</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - Капитализация (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Капитализация (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - Объем торгов</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Объем торгов</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Объем торгов (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - Экспорт</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Экспорт</t>
-        </is>
-      </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>Индия - Экспорт (сезонность устранена) STL</t>
-        </is>
-      </c>
-      <c r="T3" s="1" t="inlineStr">
-        <is>
-          <t>Китай - Экспорт (сезонность устранена) STL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>report_date</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="2">
         <v>36525</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>207756762196.7517</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>612624244538.9901</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>195404384464.375</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>547587036999.4947</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>471791257337.7126</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>2141029306650.873</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>473653882851.8411</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>2128416183028.412</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>345465134113.5591</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>622080229847.0482</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>379727262840.2844</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>700876154565.6168</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>89484695191.10597</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5">
         <v>223608146123.6073</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>17153166243.01357</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R5">
         <v>109572605168.017</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S5">
         <v>17800464539.6492</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5">
         <v>109600858890.7168</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="6" spans="1:20">
+      <c r="A6" s="2">
         <v>36616</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>215174267884.4943</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>486242360395.8081</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>201238636011.4337</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>551674386631.0248</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>495048586909.7173</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>2159135788816.74</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>490387059094.9519</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>2175224021606.861</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>444427522478.0953</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>824248194574.6842</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>395993751028.5477</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>826948467936.5413</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>248953504311.4536</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>426969353316.4083</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P6">
         <v>388656269384.4274</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>19004410847.36344</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R6">
         <v>96523261638.44374</v>
       </c>
-      <c r="S6" t="n">
+      <c r="S6">
         <v>18830715756.89885</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T6">
         <v>106871761272.9569</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
+    <row r="7" spans="1:20">
+      <c r="A7" s="2">
         <v>36707</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>192619030201.7278</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>557208140741.9221</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>200229489761.121</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>572024141913.7999</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>507501055803.7451</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>2176948865228.2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>499735635494.646</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2173829459714.147</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>364281554291.4902</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>933917110347.8738</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>349692196783.9368</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>854374257117.0016</v>
       </c>
-      <c r="N7" t="n">
+      <c r="N7">
         <v>189885623878.0342</v>
       </c>
-      <c r="O7" t="n">
+      <c r="O7">
         <v>367712662382.3112</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7">
         <v>293037975807.3193</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7">
         <v>19490926534.34342</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R7">
         <v>119317585241.7569</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S7">
         <v>20036772572.78334</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7">
         <v>117702212843.5883</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
+    <row r="8" spans="1:20">
+      <c r="A8" s="2">
         <v>36799</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>183725988819.6903</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>598204243829.6273</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>202206220650.1378</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>583739059944.5073</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>508954187287.2709</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>2210878711262.481</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>518892833632.2941</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>2205755072509.482</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>309254466357.0552</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>963833887302.4944</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>340720491753.4516</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>972830053723.7256</v>
       </c>
-      <c r="N8" t="n">
+      <c r="N8">
         <v>281676397941.0567</v>
       </c>
-      <c r="O8" t="n">
+      <c r="O8">
         <v>334003831220.3302</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8">
         <v>329760459065.6849</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>21261006380.85041</v>
       </c>
-      <c r="R8" t="n">
+      <c r="R8">
         <v>129243650028.185</v>
       </c>
-      <c r="S8" t="n">
+      <c r="S8">
         <v>20533169738.73451</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8">
         <v>120605896410.0993</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
+    <row r="9" spans="1:20">
+      <c r="A9" s="2">
         <v>36891</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>217810557559.7396</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>667356277768.0151</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>205544896851.54</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>598224688457.8715</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>532443658273.9376</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>2248865914048.984</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>536215671328.0781</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>2245361612003.398</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>318862844280.4709</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>1088345789529.94</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>333585440795.1542</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>1152910470017.163</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N9">
         <v>261447016908.1327</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9">
         <v>257361924957.1247</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9">
         <v>362993979649.3716</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>21466047071.46363</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R9">
         <v>125401689365.8589</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S9">
         <v>22109121941.09399</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9">
         <v>122160069713.6648</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
+    <row r="10" spans="1:20">
+      <c r="A10" s="2">
         <v>36981</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>220404709442.0931</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>546223258848.5228</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>206843755209.4471</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>615488657534.5078</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>556406482480.061</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>2294812219342.443</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>550117398945.313</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>2308768174338.042</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>278345309626.7345</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>1140084568995.086</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>249027136384.2883</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>1132631021361.728</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N10">
         <v>256590844922.6967</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O10">
         <v>225309661432.0511</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10">
         <v>191662834007.6526</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>22991677061.39441</v>
       </c>
-      <c r="R10" t="n">
+      <c r="R10">
         <v>109858420843.3992</v>
       </c>
-      <c r="S10" t="n">
+      <c r="S10">
         <v>22177251988.92427</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10">
         <v>124765491278.3543</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
+    <row r="11" spans="1:20">
+      <c r="A11" s="2">
         <v>37072</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>203449845549.8907</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>610544078226.0837</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>210789635392.6172</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>626970877030.0626</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>568203306835.3314</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>2407877754507.649</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>560474515814.2333</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>2400050438843.256</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>237000723001.8585</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>1211933769119.025</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>232682047344.5639</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>1151351258533.633</v>
       </c>
-      <c r="N11" t="n">
+      <c r="N11">
         <v>86482881808.89049</v>
       </c>
-      <c r="O11" t="n">
+      <c r="O11">
         <v>333898124673.6207</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P11">
         <v>268474289941.9968</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>20206726473.03037</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R11">
         <v>122863878645.8305</v>
       </c>
-      <c r="S11" t="n">
+      <c r="S11">
         <v>20898436708.0617</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T11">
         <v>121668828462.6324</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
+    <row r="12" spans="1:20">
+      <c r="A12" s="2">
         <v>37164</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>191994659369.7722</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>654925338282.0624</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>210415471349.1873</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>639321357075.4884</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>561642510855.1316</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>2490033356733.388</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>571341808881.7267</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>2482837101044.472</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>184604631672.0153</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>1047928069152.48</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>207178433938.3067</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>1056746008132.557</v>
       </c>
-      <c r="N12" t="n">
+      <c r="N12">
         <v>59981598193.45992</v>
       </c>
-      <c r="O12" t="n">
+      <c r="O12">
         <v>168241636422.7155</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P12">
         <v>174642807726.6298</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>20636242688.00402</v>
       </c>
-      <c r="R12" t="n">
+      <c r="R12">
         <v>133177577008.5815</v>
       </c>
-      <c r="S12" t="n">
+      <c r="S12">
         <v>20426631510.09927</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T12">
         <v>123014352664.1173</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
+    <row r="13" spans="1:20">
+      <c r="A13" s="2">
         <v>37256</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>227949759493.8207</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>727130745726.493</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>215786239332.5813</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>653588160054.7141</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>573795215640.004</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>2545196686717.861</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>579539209832.7096</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>2550929547769.133</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>213087273616.4919</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>986269672878.4629</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>208593680745.4961</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>1035902959939.026</v>
       </c>
-      <c r="N13" t="n">
+      <c r="N13">
         <v>83375686477.55385</v>
       </c>
-      <c r="O13" t="n">
+      <c r="O13">
         <v>138824498854.2834</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P13">
         <v>218703233655.1537</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q13">
         <v>20251633103.66082</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13">
         <v>133720367346.3522</v>
       </c>
-      <c r="S13" t="n">
+      <c r="S13">
         <v>20890429247.52077</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T13">
         <v>127094567747.8677</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
+    <row r="14" spans="1:20">
+      <c r="A14" s="2">
         <v>37346</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>227298484288.8767</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>600705994856.7214</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>213890804650.0157</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>674055031176.3932</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>595074876358.0145</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2618880800722.574</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>587013020501.3358</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>2630239300504.905</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>246468544555.0721</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>969801387025.3722</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>234961027278.9386</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>953572586488.3121</v>
       </c>
-      <c r="N14" t="n">
+      <c r="N14">
         <v>103029407406.6127</v>
       </c>
-      <c r="O14" t="n">
+      <c r="O14">
         <v>177816185382.4479</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P14">
         <v>148400992323.1567</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>23329046921.31525</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14">
         <v>120556673460.8784</v>
       </c>
-      <c r="S14" t="n">
+      <c r="S14">
         <v>21858621765.5013</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T14">
         <v>140113046777.2619</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
+    <row r="15" spans="1:20">
+      <c r="A15" s="2">
         <v>37437</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>210467246583.4827</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>674468580482.4915</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>217539379243.5987</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>692333760640.038</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>634762521728.1831</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>2764859448128.101</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>627149501983.6873</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>2752624737424.65</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>253846900550.6306</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>1089542477937.221</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>259514291779.5956</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>1048432897925.875</v>
       </c>
-      <c r="N15" t="n">
+      <c r="N15">
         <v>92686150426.93335</v>
       </c>
-      <c r="O15" t="n">
+      <c r="O15">
         <v>204379895141.7107</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15">
         <v>147457091944.1172</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>23539288488.90361</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15">
         <v>146185184954.6917</v>
       </c>
-      <c r="S15" t="n">
+      <c r="S15">
         <v>24340587135.95797</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15">
         <v>145323621154.8647</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="n">
+    <row r="16" spans="1:20">
+      <c r="A16" s="2">
         <v>37529</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>201952104400.8441</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>729054082884.0259</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>220470766251.136</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>712483184275.2418</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>628134943095.0813</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>2909519452057.962</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>637399234531.1202</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>2900167559089.019</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>221821894812.3402</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>1018679095528.589</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>235385380737.0889</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>1029994678342.533</v>
       </c>
-      <c r="N16" t="n">
+      <c r="N16">
         <v>85152334203.61441</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O16">
         <v>147938672553.8496</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16">
         <v>165542769826.6428</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16">
         <v>25689048598.57923</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16">
         <v>172575921137.1964</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S16">
         <v>26003916426.92016</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16">
         <v>160703803558.2937</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
+    <row r="17" spans="1:20">
+      <c r="A17" s="2">
         <v>37621</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>231884340556.1588</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>807696554675.4263</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>219806583713.871</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>729505670965.0792</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>642509207462.4349</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>2993044306513.747</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>650421706654.3398</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>3008724588422.356</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>242679397336.2907</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>873770576039.7234</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>220043970445.5545</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>907704412833.3107</v>
       </c>
-      <c r="N17" t="n">
+      <c r="N17">
         <v>96353101130.73871</v>
       </c>
-      <c r="O17" t="n">
+      <c r="O17">
         <v>107613007879.2012</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17">
         <v>163861407773.9396</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17">
         <v>23838439872.18652</v>
       </c>
-      <c r="R17" t="n">
+      <c r="R17">
         <v>175566459341.2713</v>
       </c>
-      <c r="S17" t="n">
+      <c r="S17">
         <v>24493737667.35075</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17">
         <v>165636316067.461</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
+    <row r="18" spans="1:20">
+      <c r="A18" s="2">
         <v>37711</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>237864178976.8425</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>678975192720.7848</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>224418863665.6164</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>756692156945.2087</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>670250032021.097</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>3126410580487.526</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18">
         <v>660400536334.6796</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>3135932093314.687</v>
       </c>
-      <c r="J18" t="n">
+      <c r="J18">
         <v>221957912188.5551</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>958061613788.7087</v>
       </c>
-      <c r="L18" t="n">
+      <c r="L18">
         <v>226961685476.9136</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M18">
         <v>934268560842.7321</v>
       </c>
-      <c r="N18" t="n">
+      <c r="N18">
         <v>89538653809.43275</v>
       </c>
-      <c r="O18" t="n">
+      <c r="O18">
         <v>149605206069.8993</v>
       </c>
-      <c r="P18" t="n">
+      <c r="P18">
         <v>123871825290.2019</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="Q18">
         <v>26472927820.72755</v>
       </c>
-      <c r="R18" t="n">
+      <c r="R18">
         <v>160203449944.7337</v>
       </c>
-      <c r="S18" t="n">
+      <c r="S18">
         <v>24363442421.51428</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T18">
         <v>184511751526.7527</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
+    <row r="19" spans="1:20">
+      <c r="A19" s="2">
         <v>37802</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>220726019969.0784</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>748138683797.5447</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>227613577567.4138</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>767371352126.446</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>674454847811.8176</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>3383744184890.913</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H19">
         <v>666920771382.4441</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>3367047152989.548</v>
       </c>
-      <c r="J19" t="n">
+      <c r="J19">
         <v>279113924600.9062</v>
       </c>
-      <c r="K19" t="n">
+      <c r="K19">
         <v>944401504827.3263</v>
       </c>
-      <c r="L19" t="n">
+      <c r="L19">
         <v>293884496636.3419</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M19">
         <v>918905033334.5858</v>
       </c>
-      <c r="N19" t="n">
+      <c r="N19">
         <v>88745356056.87085</v>
       </c>
-      <c r="O19" t="n">
+      <c r="O19">
         <v>257568895769.6102</v>
       </c>
-      <c r="P19" t="n">
+      <c r="P19">
         <v>207083997267.5637</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="Q19">
         <v>23978920886.50616</v>
       </c>
-      <c r="R19" t="n">
+      <c r="R19">
         <v>195160839759.039</v>
       </c>
-      <c r="S19" t="n">
+      <c r="S19">
         <v>24837744563.47014</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T19">
         <v>194741459125.6391</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
+    <row r="20" spans="1:20">
+      <c r="A20" s="2">
         <v>37894</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>218618463213.4142</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>817180293990.5966</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>237399320323.8147</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>799856705987.8636</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>667096896247.3379</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>3564424994768.901</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20">
         <v>675679600702.2096</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>3552350796406.122</v>
       </c>
-      <c r="J20" t="n">
+      <c r="J20">
         <v>342899250486.675</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>892609424826.5972</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L20">
         <v>347287170079.3342</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M20">
         <v>906509247789.7413</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N20">
         <v>143527456635.3242</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O20">
         <v>124413475704.3941</v>
       </c>
-      <c r="P20" t="n">
+      <c r="P20">
         <v>154028999094.9656</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="Q20">
         <v>25325277862.91693</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R20">
         <v>222068709387.5213</v>
       </c>
-      <c r="S20" t="n">
+      <c r="S20">
         <v>26142201428.67042</v>
       </c>
-      <c r="T20" t="n">
+      <c r="T20">
         <v>208363258314.6873</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
+    <row r="21" spans="1:20">
+      <c r="A21" s="2">
         <v>37986</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>257944583651.4306</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>896031763547.3755</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>246093248813.4047</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>812882738134.3497</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>681926161522.3323</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>3531728072334.431</v>
       </c>
-      <c r="H21" t="n">
+      <c r="H21">
         <v>692202448755.5225</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>3556776520632.253</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J21">
         <v>467547765939.91</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>943098464793.4517</v>
       </c>
-      <c r="L21" t="n">
+      <c r="L21">
         <v>430022591521.8453</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M21">
         <v>964014695130.8848</v>
       </c>
-      <c r="N21" t="n">
+      <c r="N21">
         <v>176137639269.8353</v>
       </c>
-      <c r="O21" t="n">
+      <c r="O21">
         <v>191929544838.4385</v>
       </c>
-      <c r="P21" t="n">
+      <c r="P21">
         <v>234702397190.8835</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="Q21">
         <v>28284002241.12905</v>
       </c>
-      <c r="R21" t="n">
+      <c r="R21">
         <v>240385274158.6804</v>
       </c>
-      <c r="S21" t="n">
+      <c r="S21">
         <v>29016624047.56157</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T21">
         <v>227384995583.5667</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
+    <row r="22" spans="1:20">
+      <c r="A22" s="2">
         <v>38077</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>255989970376.1833</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>766011826345.05</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>242209973578.6123</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>848940418844.3156</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>716264976674.3854</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>3653403466270.624</v>
       </c>
-      <c r="H22" t="n">
+      <c r="H22">
         <v>704531071390.8333</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>3659992875851.072</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J22">
         <v>574306749592.0905</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K22">
         <v>1100050169837.664</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L22">
         <v>593645870629.3904</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M22">
         <v>1066357854095.263</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N22">
         <v>192339097426.9243</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O22">
         <v>358168481864.1223</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P22">
         <v>326461177723.5831</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q22">
         <v>32563179086.47504</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R22">
         <v>208982335011.8679</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S22">
         <v>29889083735.93539</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T22">
         <v>238624749593.1076</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
+    <row r="23" spans="1:20">
+      <c r="A23" s="2">
         <v>38168</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>252233758126.4325</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>853595438431.0002</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>259197377425.9598</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>874197306432.3495</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>720334643157.7708</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>3694870573008.512</v>
       </c>
-      <c r="H23" t="n">
+      <c r="H23">
         <v>713368775466.9845</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>3673019322493.453</v>
       </c>
-      <c r="J23" t="n">
+      <c r="J23">
         <v>387576914260.352</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K23">
         <v>878740780630.9595</v>
       </c>
-      <c r="L23" t="n">
+      <c r="L23">
         <v>410983678848.8712</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M23">
         <v>869254491358.5509</v>
       </c>
-      <c r="N23" t="n">
+      <c r="N23">
         <v>152651466504.8079</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O23">
         <v>209223679751.128</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P23">
         <v>163595221988.6382</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q23">
         <v>29380492743.24075</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R23">
         <v>256470932017.9099</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S23">
         <v>30259113421.4623</v>
       </c>
-      <c r="T23" t="n">
+      <c r="T23">
         <v>256483799985.0208</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
+    <row r="24" spans="1:20">
+      <c r="A24" s="2">
         <v>38260</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>250116371892.5675</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>921903470660.8307</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>269280999213.8531</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>904011165808.5972</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>715468764508.6957</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>3767560905088.325</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24">
         <v>723367185683.4194</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>3754074157486.946</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J24">
         <v>472773751611.3206</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>888904797281.0433</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L24">
         <v>466302190224.7313</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M24">
         <v>911248842076.5688</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N24">
         <v>139469645815.4021</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O24">
         <v>181081144969.033</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P24">
         <v>222947857632.9502</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q24">
         <v>31201988687.42157</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R24">
         <v>284389093284.1149</v>
       </c>
-      <c r="S24" t="n">
+      <c r="S24">
         <v>32525917463.14347</v>
       </c>
-      <c r="T24" t="n">
+      <c r="T24">
         <v>268613652801.3083</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="n">
+    <row r="25" spans="1:20">
+      <c r="A25" s="2">
         <v>38352</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>276701911463.3738</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>1021767201260.819</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>264694394910.8554</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>930173268721.1389</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>748426798878.7899</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>3821658588898.661</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H25">
         <v>761763744589.3658</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>3857416656461.925</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J25">
         <v>604910924977.1101</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>798437867096.5006</v>
       </c>
-      <c r="L25" t="n">
+      <c r="L25">
         <v>556816492165.3893</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M25">
         <v>808637423444.1827</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N25">
         <v>141247368146.5703</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O25">
         <v>171509581303.6862</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P25">
         <v>229603045627.0437</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q25">
         <v>33788406358.99426</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R25">
         <v>316068772759.3026</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S25">
         <v>34559333836.23444</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T25">
         <v>299524828188.5999</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
+    <row r="26" spans="1:20">
+      <c r="A26" s="2">
         <v>38442</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>289703393729.8419</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>872347633147.3751</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>274871782297.6053</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>964926143182.9126</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>785869936368.1805</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>3938410279226.177</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H26">
         <v>769403396266.0793</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>3942832149435.018</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J26">
         <v>607827278482.7532</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K26">
         <v>739061937023.3228</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L26">
         <v>643454093030.6669</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M26">
         <v>693665821693.3386</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N26">
         <v>166673708504.4026</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O26">
         <v>142328530533.3518</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P26">
         <v>59110962282.82266</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q26">
         <v>41287476362.55695</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R26">
         <v>274001791255.6669</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S26">
         <v>38206048765.5185</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T26">
         <v>309906839026.8389</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="n">
+    <row r="27" spans="1:20">
+      <c r="A27" s="2">
         <v>38533</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>276269625174.9617</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>970982196777.9115</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>283573724276.6989</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>990379789656.1046</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>814625992379.5635</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>3981872235544.116</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H27">
         <v>810107642610.1605</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>3949882515869.707</v>
       </c>
-      <c r="J27" t="n">
+      <c r="J27">
         <v>658445963464.1503</v>
       </c>
-      <c r="K27" t="n">
+      <c r="K27">
         <v>675627285085.4072</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L27">
         <v>686382911412.8196</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M27">
         <v>657674230578.2781</v>
       </c>
-      <c r="N27" t="n">
+      <c r="N27">
         <v>149604573562.9583</v>
       </c>
-      <c r="O27" t="n">
+      <c r="O27">
         <v>160585017517.6207</v>
       </c>
-      <c r="P27" t="n">
+      <c r="P27">
         <v>112182903483.5493</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q27">
         <v>36540219752.12605</v>
       </c>
-      <c r="R27" t="n">
+      <c r="R27">
         <v>330195254521.0214</v>
       </c>
-      <c r="S27" t="n">
+      <c r="S27">
         <v>37258951810.38126</v>
       </c>
-      <c r="T27" t="n">
+      <c r="T27">
         <v>329838443111.6458</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="n">
+    <row r="28" spans="1:20">
+      <c r="A28" s="2">
         <v>38625</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>261931161409.3625</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>1043640661965.102</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>282571892594.8603</v>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>1025641494325.001</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>822388533669.8273</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>4093421776825.26</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H28">
         <v>830344479415.5356</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>4077882572722.611</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J28">
         <v>784875744407.0564</v>
       </c>
-      <c r="K28" t="n">
+      <c r="K28">
         <v>715336238302.8269</v>
       </c>
-      <c r="L28" t="n">
+      <c r="L28">
         <v>767890754022.3425</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M28">
         <v>803853988197.2721</v>
       </c>
-      <c r="N28" t="n">
+      <c r="N28">
         <v>220400399629.8414</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28">
         <v>233590843071.324</v>
       </c>
-      <c r="P28" t="n">
+      <c r="P28">
         <v>314956599350.7968</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q28">
         <v>37304591837.51424</v>
       </c>
-      <c r="R28" t="n">
+      <c r="R28">
         <v>356267076427.7675</v>
       </c>
-      <c r="S28" t="n">
+      <c r="S28">
         <v>39097597755.89481</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T28">
         <v>336469554865.2709</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
+    <row r="29" spans="1:20">
+      <c r="A29" s="2">
         <v>38717</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>302028462497.9444</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>1163579275455.342</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>289136109549.996</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>1061318751501.103</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>828087271278.4478</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>4137916790283.959</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H29">
         <v>844136238190.8584</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>4186263798660.167</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J29">
         <v>850421640480.8772</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K29">
         <v>689267705871.0671</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L29">
         <v>799679773713.173</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M29">
         <v>702141348408.8348</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N29">
         <v>194496260969.2692</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O29">
         <v>139382167337.0106</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P29">
         <v>207436480494.0383</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q29">
         <v>38993079774.59834</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R29">
         <v>370591795756.1896</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S29">
         <v>39764521865.87308</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T29">
         <v>351621869814.4564</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
+    <row r="30" spans="1:20">
+      <c r="A30" s="2">
         <v>38807</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>318252685622.6609</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>1001578828521.794</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>302479063984.4141</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>1108105677913.604</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>895621268149.4822</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>4321829491016.126</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H30">
         <v>873993179855.3429</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>4336411709987.082</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J30">
         <v>1034945512334.114</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K30">
         <v>740043407203.4421</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L30">
         <v>1084685118302.033</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M30">
         <v>705770164594.0405</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N30">
         <v>261020544766.5505</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O30">
         <v>234407204242.3701</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P30">
         <v>89601957809.2139</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q30">
         <v>45295695380.08461</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R30">
         <v>332285021277.8229</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S30">
         <v>41914665120.48232</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T30">
         <v>374670402653.533</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
+    <row r="31" spans="1:20">
+      <c r="A31" s="2">
         <v>38898</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>288168618794.2024</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>1123775543388.201</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>295547725445.6137</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>1140437581626.971</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>902507770977.2402</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>4529634488061.231</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H31">
         <v>899817684019.9468</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>4480787999251.628</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J31">
         <v>914111509011.2136</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K31">
         <v>929916407445.4576</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L31">
         <v>942963905016.8258</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M31">
         <v>893168867363.1614</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N31">
         <v>263547940502.7215</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O31">
         <v>565492942888.3192</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P31">
         <v>521249143236.1832</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q31">
         <v>44557091204.78883</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R31">
         <v>390009071938.1456</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S31">
         <v>45084671184.61716</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T31">
         <v>388595365655.08</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
+    <row r="32" spans="1:20">
+      <c r="A32" s="2">
         <v>38990</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>283653381214.9045</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>1199029101299.163</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>305826285227.9703</v>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>1180616069363.935</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>928442440716.2378</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>4664310038994.511</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H32">
         <v>937154315265.3378</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>4636352658399.658</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J32">
         <v>1044136227304.626</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K32">
         <v>1103274112461.398</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L32">
         <v>1016559573112.809</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M32">
         <v>1266348767657.502</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N32">
         <v>191106969063.7892</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O32">
         <v>425050563054.9023</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P32">
         <v>590789570283.0486</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q32">
         <v>48826498663.8038</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R32">
         <v>441634509225.2893</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S32">
         <v>50698637750.64374</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T32">
         <v>415878243426.0793</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
+    <row r="33" spans="1:20">
+      <c r="A33" s="2">
         <v>39082</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>325879315396.5848</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>1345104371843.81</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>312089328018.5969</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>1229348129759.572</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>924463466523.0188</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>4697387337314.942</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H33">
         <v>942111535188.4468</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>4761823730538.154</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J33">
         <v>1162973385801.56</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K33">
         <v>1864146368075.365</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L33">
         <v>1118395982627.612</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M33">
         <v>1820710903425.629</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N33">
         <v>242310903064.2838</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O33">
         <v>672498818196.8148</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P33">
         <v>777627652084.7018</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q33">
         <v>44364668851.59357</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R33">
         <v>455940726810.176</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S33">
         <v>45203886315.17398</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T33">
         <v>436936197866.2102</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
+    <row r="34" spans="1:20">
+      <c r="A34" s="2">
         <v>39172</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>332956751737.1529</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>1183663663595.625</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>316841051914.5313</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>1307118052753.964</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>999727954830.205</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>4882675891218.114</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H34">
         <v>974291879216.9305</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>4920221685826.66</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J34">
         <v>1134544893335.949</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>2609278040939.007</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L34">
         <v>1187792354075.416</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M34">
         <v>2561771752424.533</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N34">
         <v>248820913420.1262</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O34">
         <v>1529135482364.525</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P34">
         <v>1326077365580.107</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q34">
         <v>48608429695.44479</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R34">
         <v>398824266958.1501</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S34">
         <v>45468025370.74976</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T34">
         <v>447366223583.8767</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
+    <row r="35" spans="1:20">
+      <c r="A35" s="2">
         <v>39263</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>313774417598.6384</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>1335120041942.376</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>321047985066.0892</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>1350148578761.909</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>988064478293.1769</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>5092518946930.648</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H35">
         <v>986073235828.4609</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>5021760057926.328</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J35">
         <v>1316766860766.837</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K35">
         <v>3375473015151.071</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L35">
         <v>1344877196195.129</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M35">
         <v>3326831447448.367</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N35">
         <v>266061461037.4502</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O35">
         <v>3292520527268.875</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P35">
         <v>3252406842973.03</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q35">
         <v>46714626520.59304</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R35">
         <v>459482620941.9811</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S35">
         <v>47193755528.89807</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T35">
         <v>456485408530.4041</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
+    <row r="36" spans="1:20">
+      <c r="A36" s="2">
         <v>39355</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>302712183660.5839</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>1400862512638.569</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>325301957953.5343</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>1380689189356.021</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>1009032830526.714</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>5146272201257.118</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36">
         <v>1019183386114.521</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>5100438821430.97</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J36">
         <v>1598198923307.406</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K36">
         <v>5030749429433.417</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L36">
         <v>1561291275203.225</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M36">
         <v>5259506418064.887</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N36">
         <v>343512598384.7152</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O36">
         <v>2662623507780.966</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P36">
         <v>2827166806820.946</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q36">
         <v>46899849452.34867</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R36">
         <v>497939094713.968</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S36">
         <v>48618333024.88237</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T36">
         <v>467755821066.3587</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
+    <row r="37" spans="1:20">
+      <c r="A37" s="2">
         <v>39447</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>368713244011.4489</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>1560209123974.015</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>354784850177.1257</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>1429409745021.452</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>1020085536186.275</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>5112987435028.791</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H37">
         <v>1037926858807.557</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>5187457143336.396</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J37">
         <v>2180499754096.726</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>6391767493212.358</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L37">
         <v>2137066101474.387</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M37">
         <v>6282056359101.691</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N37">
         <v>537995414421.5282</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O37">
         <v>1746485026180.604</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P37">
         <v>1906339836234.202</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q37">
         <v>50657585746.5472</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R37">
         <v>493263868707.2308</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S37">
         <v>51685605534.65719</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T37">
         <v>474853401811.8555</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
+    <row r="38" spans="1:20">
+      <c r="A38" s="2">
         <v>39538</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>359709787192.2313</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>1331217497679.413</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>344193328613.686</v>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>1473228899296.574</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>1103242345692.239</v>
       </c>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>5184636245177.896</v>
       </c>
-      <c r="H38" t="n">
+      <c r="H38">
         <v>1077685561213.919</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>5245831448461.534</v>
       </c>
-      <c r="J38" t="n">
+      <c r="J38">
         <v>1547152530655.208</v>
       </c>
-      <c r="K38" t="n">
+      <c r="K38">
         <v>4275702986212.449</v>
       </c>
-      <c r="L38" t="n">
+      <c r="L38">
         <v>1602269731181.832</v>
       </c>
-      <c r="M38" t="n">
+      <c r="M38">
         <v>4195053046223.868</v>
       </c>
-      <c r="N38" t="n">
+      <c r="N38">
         <v>421070230784.8575</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O38">
         <v>1813198731268.214</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P38">
         <v>1544179725648.891</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q38">
         <v>56705170005.73008</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R38">
         <v>413182973982.1636</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S38">
         <v>53875772786.01504</v>
       </c>
-      <c r="T38" t="n">
+      <c r="T38">
         <v>467031044501.7353</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
+    <row r="39" spans="1:20">
+      <c r="A39" s="2">
         <v>39629</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>371461928616.8564</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>1505370901213.931</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>378285200329.9753</v>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>1519978885876.562</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>1096581234474.948</v>
       </c>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>5387809899299.296</v>
       </c>
-      <c r="H39" t="n">
+      <c r="H39">
         <v>1092766460340.506</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>5299359350086.229</v>
       </c>
-      <c r="J39" t="n">
+      <c r="J39">
         <v>1282649497257.897</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39">
         <v>3351577013993.253</v>
       </c>
-      <c r="L39" t="n">
+      <c r="L39">
         <v>1311882571671.225</v>
       </c>
-      <c r="M39" t="n">
+      <c r="M39">
         <v>3286346618166.442</v>
       </c>
-      <c r="N39" t="n">
+      <c r="N39">
         <v>341038244458.255</v>
       </c>
-      <c r="O39" t="n">
+      <c r="O39">
         <v>1377636835918.528</v>
       </c>
-      <c r="P39" t="n">
+      <c r="P39">
         <v>1341680687455.394</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q39">
         <v>68818065197.08635</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R39">
         <v>472098623797.4454</v>
       </c>
-      <c r="S39" t="n">
+      <c r="S39">
         <v>69167257782.03439</v>
       </c>
-      <c r="T39" t="n">
+      <c r="T39">
         <v>467236865747.665</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
+    <row r="40" spans="1:20">
+      <c r="A40" s="2">
         <v>39721</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>357827894615.0875</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>1578778884883.189</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>380631937684.8698</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>1555010026293.389</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>1100377635410.81</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>5594374088437.472</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H40">
         <v>1114408695473.105</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>5529155303638.692</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J40">
         <v>1173355222143.548</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K40">
         <v>2795779964564.113</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L40">
         <v>1129138889962.004</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M40">
         <v>3097560307538.924</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N40">
         <v>316342877558.6016</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O40">
         <v>877327937504.3101</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P40">
         <v>973602677125.3525</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q40">
         <v>64709371987.71143</v>
       </c>
-      <c r="R40" t="n">
+      <c r="R40">
         <v>526558639301.2233</v>
       </c>
-      <c r="S40" t="n">
+      <c r="S40">
         <v>66321650639.88641</v>
       </c>
-      <c r="T40" t="n">
+      <c r="T40">
         <v>493531674996.6762</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="n">
+    <row r="41" spans="1:20">
+      <c r="A41" s="2">
         <v>39813</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>385484340849.7358</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>1715637872532.766</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>371684371658.8128</v>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>1568738908910.501</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>1148159882370.751</v>
       </c>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>5778688145517.008</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H41">
         <v>1164194911473.977</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>5854352638393.691</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J41">
         <v>867858036428.8981</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41">
         <v>2311638662357.48</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L41">
         <v>823599633635.983</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M41">
         <v>2174091202124.255</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N41">
         <v>227387811512.1122</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O41">
         <v>967159096816.5424</v>
       </c>
-      <c r="P41" t="n">
+      <c r="P41">
         <v>1169978169306.974</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q41">
         <v>52011630059.61816</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R41">
         <v>461404880861.3869</v>
       </c>
-      <c r="S41" t="n">
+      <c r="S41">
         <v>53265027595.17636</v>
       </c>
-      <c r="T41" t="n">
+      <c r="T41">
         <v>442998867733.8976</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="n">
+    <row r="42" spans="1:20">
+      <c r="A42" s="2">
         <v>39903</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>377065010722.0817</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>1429368750315.732</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>362493973339.8058</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>1590876241580.177</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>1241387373208.641</v>
       </c>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>6631724382645.917</v>
       </c>
-      <c r="H42" t="n">
+      <c r="H42">
         <v>1216338995599.754</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>6714510687930.558</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J42">
         <v>849742722466.4816</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42">
         <v>3063475628285.435</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L42">
         <v>907569224569.9122</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M42">
         <v>2963456580383.18</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N42">
         <v>203072901230.5327</v>
       </c>
-      <c r="O42" t="n">
+      <c r="O42">
         <v>1757964896967.632</v>
       </c>
-      <c r="P42" t="n">
+      <c r="P42">
         <v>1445588348601.729</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="Q42">
         <v>51720027024.65041</v>
       </c>
-      <c r="R42" t="n">
+      <c r="R42">
         <v>318575464664.9374</v>
       </c>
-      <c r="S42" t="n">
+      <c r="S42">
         <v>48561487617.77882</v>
       </c>
-      <c r="T42" t="n">
+      <c r="T42">
         <v>377392433917.6611</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="n">
+    <row r="43" spans="1:20">
+      <c r="A43" s="2">
         <v>39994</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>369925177394.0525</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>1631834777686.977</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>375151422299.4476</v>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>1646990949089.042</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>1264322909952.232</v>
       </c>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>7216043297909.125</v>
       </c>
-      <c r="H43" t="n">
+      <c r="H43">
         <v>1256877520159.303</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>7120121691897.885</v>
       </c>
-      <c r="J43" t="n">
+      <c r="J43">
         <v>1279073930937.322</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43">
         <v>3851299132656.453</v>
       </c>
-      <c r="L43" t="n">
+      <c r="L43">
         <v>1311853428598.284</v>
       </c>
-      <c r="M43" t="n">
+      <c r="M43">
         <v>3779262763723.856</v>
       </c>
-      <c r="N43" t="n">
+      <c r="N43">
         <v>405836984317.8452</v>
       </c>
-      <c r="O43" t="n">
+      <c r="O43">
         <v>2462095219485.456</v>
       </c>
-      <c r="P43" t="n">
+      <c r="P43">
         <v>2440372067422.152</v>
       </c>
-      <c r="Q43" t="n">
+      <c r="Q43">
         <v>50417825888.47513</v>
       </c>
-      <c r="R43" t="n">
+      <c r="R43">
         <v>360513845924.1121</v>
       </c>
-      <c r="S43" t="n">
+      <c r="S43">
         <v>50748791818.50601</v>
       </c>
-      <c r="T43" t="n">
+      <c r="T43">
         <v>353025301710.2212</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
+    <row r="44" spans="1:20">
+      <c r="A44" s="2">
         <v>40086</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>358845090582.2421</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>1745506123854.761</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>381701401089.3814</v>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>1716739004350.677</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>1215392725715.933</v>
       </c>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>7461505452490.65</v>
       </c>
-      <c r="H44" t="n">
+      <c r="H44">
         <v>1234223733362.411</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>7383007893818.403</v>
       </c>
-      <c r="J44" t="n">
+      <c r="J44">
         <v>1438903708061.44</v>
       </c>
-      <c r="K44" t="n">
+      <c r="K44">
         <v>3763200549830.326</v>
       </c>
-      <c r="L44" t="n">
+      <c r="L44">
         <v>1389707918434.116</v>
       </c>
-      <c r="M44" t="n">
+      <c r="M44">
         <v>4094945237910.528</v>
       </c>
-      <c r="N44" t="n">
+      <c r="N44">
         <v>388213262501.5358</v>
       </c>
-      <c r="O44" t="n">
+      <c r="O44">
         <v>3161578504110.867</v>
       </c>
-      <c r="P44" t="n">
+      <c r="P44">
         <v>3254504420464.496</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="Q44">
         <v>51934539877.56025</v>
       </c>
-      <c r="R44" t="n">
+      <c r="R44">
         <v>424386063881.3124</v>
       </c>
-      <c r="S44" t="n">
+      <c r="S44">
         <v>53472227475.36523</v>
       </c>
-      <c r="T44" t="n">
+      <c r="T44">
         <v>388830444053.0812</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
+    <row r="45" spans="1:20">
+      <c r="A45" s="2">
         <v>40178</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>393271224717.2269</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>1941963256482.337</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>380198202216.4562</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>1777377693762.858</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>1218772402809.853</v>
       </c>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>7572813370971.929</v>
       </c>
-      <c r="H45" t="n">
+      <c r="H45">
         <v>1232386995372.308</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>7648090335056.081</v>
       </c>
-      <c r="J45" t="n">
+      <c r="J45">
         <v>1481007094752.514</v>
       </c>
-      <c r="K45" t="n">
+      <c r="K45">
         <v>4621905376040.816</v>
       </c>
-      <c r="L45" t="n">
+      <c r="L45">
         <v>1434665618092.759</v>
       </c>
-      <c r="M45" t="n">
+      <c r="M45">
         <v>4428297112813.784</v>
       </c>
-      <c r="N45" t="n">
+      <c r="N45">
         <v>315552789456.7632</v>
       </c>
-      <c r="O45" t="n">
+      <c r="O45">
         <v>2810371504410.042</v>
       </c>
-      <c r="P45" t="n">
+      <c r="P45">
         <v>3050606605772.728</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="Q45">
         <v>52510836425.02851</v>
       </c>
-      <c r="R45" t="n">
+      <c r="R45">
         <v>459418140281.7095</v>
       </c>
-      <c r="S45" t="n">
+      <c r="S45">
         <v>54047256823.5617</v>
       </c>
-      <c r="T45" t="n">
+      <c r="T45">
         <v>440970515122.3765</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
+    <row r="46" spans="1:20">
+      <c r="A46" s="2">
         <v>40268</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>405138747386.025</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>1656555565353.67</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>390731692000.8448</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>1838784867639.376</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>1290915432595.659</v>
       </c>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>7914019171546.873</v>
       </c>
-      <c r="H46" t="n">
+      <c r="H46">
         <v>1268532503702.568</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>8010132755129.044</v>
       </c>
-      <c r="J46" t="n">
+      <c r="J46">
         <v>1472212973057.151</v>
       </c>
-      <c r="K46" t="n">
+      <c r="K46">
         <v>4552903874609.021</v>
       </c>
-      <c r="L46" t="n">
+      <c r="L46">
         <v>1518723159487.063</v>
       </c>
-      <c r="M46" t="n">
+      <c r="M46">
         <v>4439613310959.981</v>
       </c>
-      <c r="N46" t="n">
+      <c r="N46">
         <v>278780245545.6686</v>
       </c>
-      <c r="O46" t="n">
+      <c r="O46">
         <v>2159567624696.136</v>
       </c>
-      <c r="P46" t="n">
+      <c r="P46">
         <v>1859998884457.587</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q46">
         <v>56507139217.74812</v>
       </c>
-      <c r="R46" t="n">
+      <c r="R46">
         <v>401115673195.4785</v>
       </c>
-      <c r="S46" t="n">
+      <c r="S46">
         <v>53152140466.14366</v>
       </c>
-      <c r="T46" t="n">
+      <c r="T46">
         <v>465583667689.6257</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="n">
+    <row r="47" spans="1:20">
+      <c r="A47" s="2">
         <v>40359</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>391765133249.4449</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>1881226226851.761</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>395289596934.4074</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>1899795850002.282</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>1311210862008.394</v>
       </c>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>8301881956135.091</v>
       </c>
-      <c r="H47" t="n">
+      <c r="H47">
         <v>1298562000278.769</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>8206341390745.176</v>
       </c>
-      <c r="J47" t="n">
+      <c r="J47">
         <v>1514910036262.005</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47">
         <v>3631957441935.673</v>
       </c>
-      <c r="L47" t="n">
+      <c r="L47">
         <v>1552419517137.299</v>
       </c>
-      <c r="M47" t="n">
+      <c r="M47">
         <v>3589998553041.609</v>
       </c>
-      <c r="N47" t="n">
+      <c r="N47">
         <v>264624635671.3373</v>
       </c>
-      <c r="O47" t="n">
+      <c r="O47">
         <v>2046479632408.482</v>
       </c>
-      <c r="P47" t="n">
+      <c r="P47">
         <v>2028369272633.147</v>
       </c>
-      <c r="Q47" t="n">
+      <c r="Q47">
         <v>60683998478.57099</v>
       </c>
-      <c r="R47" t="n">
+      <c r="R47">
         <v>494104338418.4518</v>
       </c>
-      <c r="S47" t="n">
+      <c r="S47">
         <v>60875770190.87206</v>
       </c>
-      <c r="T47" t="n">
+      <c r="T47">
         <v>484249456970.6848</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
+    <row r="48" spans="1:20">
+      <c r="A48" s="2">
         <v>40451</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>382786906050.7279</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>1995017623382.316</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>405376891620.7914</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>1960602026073.415</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>1306645458478.52</v>
       </c>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>8565864016093.167</v>
       </c>
-      <c r="H48" t="n">
+      <c r="H48">
         <v>1328152896591.656</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>8481965797045.071</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48">
         <v>1628336186280.512</v>
       </c>
-      <c r="K48" t="n">
+      <c r="K48">
         <v>4418577032403.772</v>
       </c>
-      <c r="L48" t="n">
+      <c r="L48">
         <v>1583772274503.188</v>
       </c>
-      <c r="M48" t="n">
+      <c r="M48">
         <v>4698530859506.353</v>
       </c>
-      <c r="N48" t="n">
+      <c r="N48">
         <v>281458341564.2379</v>
       </c>
-      <c r="O48" t="n">
+      <c r="O48">
         <v>2297254645232.342</v>
       </c>
-      <c r="P48" t="n">
+      <c r="P48">
         <v>2322233882794.35</v>
       </c>
-      <c r="Q48" t="n">
+      <c r="Q48">
         <v>57017147099.42872</v>
       </c>
-      <c r="R48" t="n">
+      <c r="R48">
         <v>538515191512.042</v>
       </c>
-      <c r="S48" t="n">
+      <c r="S48">
         <v>58519177049.74506</v>
       </c>
-      <c r="T48" t="n">
+      <c r="T48">
         <v>501288942046.731</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
+    <row r="49" spans="1:20">
+      <c r="A49" s="2">
         <v>40543</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>425372890558.6884</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>2195589883012.942</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>413682516684.1761</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>2012638594215.47</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>1358144672632.25</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>8676508584540.562</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H49">
         <v>1370514776459.829</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>8748736296551.423</v>
       </c>
-      <c r="J49" t="n">
+      <c r="J49">
         <v>1627838285233.606</v>
       </c>
-      <c r="K49" t="n">
+      <c r="K49">
         <v>4805848890619.417</v>
       </c>
-      <c r="L49" t="n">
+      <c r="L49">
         <v>1578127892276.928</v>
       </c>
-      <c r="M49" t="n">
+      <c r="M49">
         <v>4601842514595.906</v>
       </c>
-      <c r="N49" t="n">
+      <c r="N49">
         <v>295172537204.2223</v>
       </c>
-      <c r="O49" t="n">
+      <c r="O49">
         <v>3527110218634.102</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P49">
         <v>3812160773320.439</v>
       </c>
-      <c r="Q49" t="n">
+      <c r="Q49">
         <v>65099536515.86562</v>
       </c>
-      <c r="R49" t="n">
+      <c r="R49">
         <v>534782922704.3835</v>
       </c>
-      <c r="S49" t="n">
+      <c r="S49">
         <v>67013988566.51615</v>
       </c>
-      <c r="T49" t="n">
+      <c r="T49">
         <v>513710053202.5091</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="n">
+    <row r="50" spans="1:20">
+      <c r="A50" s="2">
         <v>40633</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>441142297892.6997</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>1876268274232.397</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>427813875931.2523</v>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>2079521874050.015</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>1424690060012.595</v>
       </c>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>8739181815868.254</v>
       </c>
-      <c r="H50" t="n">
+      <c r="H50">
         <v>1406576791056.588</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>8836528209696.051</v>
       </c>
-      <c r="J50" t="n">
+      <c r="J50">
         <v>1498399183158.705</v>
       </c>
-      <c r="K50" t="n">
+      <c r="K50">
         <v>4904670782205.822</v>
       </c>
-      <c r="L50" t="n">
+      <c r="L50">
         <v>1536366122307.624</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M50">
         <v>4804223161173.91</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N50">
         <v>218061498369.563</v>
       </c>
-      <c r="O50" t="n">
+      <c r="O50">
         <v>2393171032862.264</v>
       </c>
-      <c r="P50" t="n">
+      <c r="P50">
         <v>2119108028823.46</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q50">
         <v>75690559303.55769</v>
       </c>
-      <c r="R50" t="n">
+      <c r="R50">
         <v>464858278099.7938</v>
       </c>
-      <c r="S50" t="n">
+      <c r="S50">
         <v>72261020966.30252</v>
       </c>
-      <c r="T50" t="n">
+      <c r="T50">
         <v>533943389067.9594</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="n">
+    <row r="51" spans="1:20">
+      <c r="A51" s="2">
         <v>40724</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>423741574205.9864</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>2121597763280.592</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>425179794161.733</v>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>2145166086334.89</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>1456675874704.053</v>
       </c>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>9029510932009.279</v>
       </c>
-      <c r="H51" t="n">
+      <c r="H51">
         <v>1438916341042.747</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>8943481476386.316</v>
       </c>
-      <c r="J51" t="n">
+      <c r="J51">
         <v>1464210958527.414</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51">
         <v>4641260120694.252</v>
       </c>
-      <c r="L51" t="n">
+      <c r="L51">
         <v>1500342123338.079</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M51">
         <v>4646147312091.973</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N51">
         <v>188791057474.062</v>
       </c>
-      <c r="O51" t="n">
+      <c r="O51">
         <v>1955721631279.976</v>
       </c>
-      <c r="P51" t="n">
+      <c r="P51">
         <v>1940541590912.117</v>
       </c>
-      <c r="Q51" t="n">
+      <c r="Q51">
         <v>74451895221.15533</v>
       </c>
-      <c r="R51" t="n">
+      <c r="R51">
         <v>542309351823.7911</v>
       </c>
-      <c r="S51" t="n">
+      <c r="S51">
         <v>74382749601.24864</v>
       </c>
-      <c r="T51" t="n">
+      <c r="T51">
         <v>531661118985.3187</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="n">
+    <row r="52" spans="1:20">
+      <c r="A52" s="2">
         <v>40816</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>397808259981.4168</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>2235470780336.315</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>420854629098.9883</v>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>2194692276559.516</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>1440765608453.437</v>
       </c>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>9200488392015.148</v>
       </c>
-      <c r="H52" t="n">
+      <c r="H52">
         <v>1463041946473.559</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>9118054097708.006</v>
       </c>
-      <c r="J52" t="n">
+      <c r="J52">
         <v>1246650997706.689</v>
       </c>
-      <c r="K52" t="n">
+      <c r="K52">
         <v>4027074170608.692</v>
       </c>
-      <c r="L52" t="n">
+      <c r="L52">
         <v>1225019138185.476</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M52">
         <v>4202717580634.897</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N52">
         <v>180081337443.5101</v>
       </c>
-      <c r="O52" t="n">
+      <c r="O52">
         <v>1763617166739.939</v>
       </c>
-      <c r="P52" t="n">
+      <c r="P52">
         <v>1707952186941.859</v>
       </c>
-      <c r="Q52" t="n">
+      <c r="Q52">
         <v>74534914598.82072</v>
       </c>
-      <c r="R52" t="n">
+      <c r="R52">
         <v>578169011199.6217</v>
       </c>
-      <c r="S52" t="n">
+      <c r="S52">
         <v>76110086937.20926</v>
       </c>
-      <c r="T52" t="n">
+      <c r="T52">
         <v>542093076865.0446</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="n">
+    <row r="53" spans="1:20">
+      <c r="A53" s="2">
         <v>40908</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>430393689760.678</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>2425535748020.127</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>419500479507.6469</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>2222256254371.058</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>1488243545072.675</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>9483135495281.158</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H53">
         <v>1500542217211.941</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>9551232213777.504</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J53">
         <v>1100832100924.541</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K53">
         <v>3716748653282.832</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L53">
         <v>1057335465388.219</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M53">
         <v>3579748460843.685</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N53">
         <v>146195728352.9171</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O53">
         <v>1266961992136.743</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P53">
         <v>1577332668836.208</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q53">
         <v>75815369625.01747</v>
       </c>
-      <c r="R53" t="n">
+      <c r="R53">
         <v>556025076974.7504</v>
       </c>
-      <c r="S53" t="n">
+      <c r="S53">
         <v>77763638756.64304</v>
       </c>
-      <c r="T53" t="n">
+      <c r="T53">
         <v>529786839853.0733</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
+    <row r="54" spans="1:20">
+      <c r="A54" s="2">
         <v>40999</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>466511593379.8488</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>2032930500802.38</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>454440450662.4592</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>2257536483216.982</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>1562068669864.022</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>9748918535899.582</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H54">
         <v>1546913817303.751</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>9839130595965.215</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J54">
         <v>1270572954233.933</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54">
         <v>3826595947286.641</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L54">
         <v>1305121486087.355</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M54">
         <v>3792855878076.151</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N54">
         <v>207873602725.2209</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O54">
         <v>1513517082257.969</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P54">
         <v>1275285199818.283</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q54">
         <v>81630453736.53554</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R54">
         <v>462040031859.4758</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S54">
         <v>77700037078.00391</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T54">
         <v>533657899020.7518</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
+    <row r="55" spans="1:20">
+      <c r="A55" s="2">
         <v>41090</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>432017913188.8362</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C55">
         <v>2281713952256.916</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>430314604169.6514</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>2309954994501.526</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>1574191621262.803</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>10194422891128.45</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H55">
         <v>1552881092324.787</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>10119333461771.94</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J55">
         <v>1215098039296.642</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K55">
         <v>3866508565751.515</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L55">
         <v>1237783122386.042</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M55">
         <v>3911753081135.037</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N55">
         <v>146420843563.9937</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O55">
         <v>1469664673213.863</v>
       </c>
-      <c r="P55" t="n">
+      <c r="P55">
         <v>1492007541396.873</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q55">
         <v>78632326257.80045</v>
       </c>
-      <c r="R55" t="n">
+      <c r="R55">
         <v>565523038616.3573</v>
       </c>
-      <c r="S55" t="n">
+      <c r="S55">
         <v>79049499064.57762</v>
       </c>
-      <c r="T55" t="n">
+      <c r="T55">
         <v>555850707693.7277</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="n">
+    <row r="56" spans="1:20">
+      <c r="A56" s="2">
         <v>41182</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>420014113105.9749</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C56">
         <v>2395580707171.949</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>443784823743.3792</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>2348849666143.163</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>1541713661691.239</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>10496185401986.17</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H56">
         <v>1564666763923.201</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>10422368207096.18</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J56">
         <v>1250969483446.363</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K56">
         <v>3650901906505.349</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L56">
         <v>1243501944917.942</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M56">
         <v>3713105979188.816</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N56">
         <v>149245953022.1648</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O56">
         <v>1231917465903.652</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P56">
         <v>1161176489996.297</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q56">
         <v>74898458914.72951</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R56">
         <v>585095800244.5439</v>
       </c>
-      <c r="S56" t="n">
+      <c r="S56">
         <v>76362202254.2119</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T56">
         <v>553263651729.6713</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="n">
+    <row r="57" spans="1:20">
+      <c r="A57" s="2">
         <v>41274</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>459943289129.1253</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C57">
         <v>2614701636163.816</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>449777453261.1336</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>2390483650807.633</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>1561733086343.636</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>10677084924887.92</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H57">
         <v>1573566058546.034</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>10747747126102.36</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J57">
         <v>1293915858074.548</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57">
         <v>3904604262650.764</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L57">
         <v>1256615808573.956</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M57">
         <v>3824378457581.158</v>
       </c>
-      <c r="N57" t="n">
+      <c r="N57">
         <v>157783052851.3431</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O57">
         <v>1143662946045.658</v>
       </c>
-      <c r="P57" t="n">
+      <c r="P57">
         <v>1426505289440.556</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q57">
         <v>73634889431.39362</v>
       </c>
-      <c r="R57" t="n">
+      <c r="R57">
         <v>591751449423.8282</v>
       </c>
-      <c r="S57" t="n">
+      <c r="S57">
         <v>75154248202.28746</v>
       </c>
-      <c r="T57" t="n">
+      <c r="T57">
         <v>558463389056.4558</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="n">
+    <row r="58" spans="1:20">
+      <c r="A58" s="2">
         <v>41364</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>465263455175.2891</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C58">
         <v>2191837493459.289</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>455042588144.9669</v>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>2437816535911.76</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>1601378565904.654</v>
       </c>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>10929160488446.15</v>
       </c>
-      <c r="H58" t="n">
+      <c r="H58">
         <v>1587535678648.553</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>11005002209108.79</v>
       </c>
-      <c r="J58" t="n">
+      <c r="J58">
         <v>1169080897063.644</v>
       </c>
-      <c r="K58" t="n">
+      <c r="K58">
         <v>3883838721800.41</v>
       </c>
-      <c r="L58" t="n">
+      <c r="L58">
         <v>1191316719584.5</v>
       </c>
-      <c r="M58" t="n">
+      <c r="M58">
         <v>3898181931786.136</v>
       </c>
-      <c r="N58" t="n">
+      <c r="N58">
         <v>158956972648.2432</v>
       </c>
-      <c r="O58" t="n">
+      <c r="O58">
         <v>1864891575931.424</v>
       </c>
-      <c r="P58" t="n">
+      <c r="P58">
         <v>1670979412316.332</v>
       </c>
-      <c r="Q58" t="n">
+      <c r="Q58">
         <v>82278160649.66109</v>
       </c>
-      <c r="R58" t="n">
+      <c r="R58">
         <v>531069142429.9832</v>
       </c>
-      <c r="S58" t="n">
+      <c r="S58">
         <v>78281545713.40111</v>
       </c>
-      <c r="T58" t="n">
+      <c r="T58">
         <v>605018682599.7275</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="n">
+    <row r="59" spans="1:20">
+      <c r="A59" s="2">
         <v>41455</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>435720614725.9144</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C59">
         <v>2439150158401.345</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>431297459378.2322</v>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>2470801208978.46</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>1626314989984.598</v>
       </c>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>11365544900594.83</v>
       </c>
-      <c r="H59" t="n">
+      <c r="H59">
         <v>1604225058305.795</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>11296556698674.62</v>
       </c>
-      <c r="J59" t="n">
+      <c r="J59">
         <v>1143142527544.451</v>
       </c>
-      <c r="K59" t="n">
+      <c r="K59">
         <v>3552589213543.014</v>
       </c>
-      <c r="L59" t="n">
+      <c r="L59">
         <v>1152021090012.009</v>
       </c>
-      <c r="M59" t="n">
+      <c r="M59">
         <v>3673737007934.945</v>
       </c>
-      <c r="N59" t="n">
+      <c r="N59">
         <v>139372171770.5244</v>
       </c>
-      <c r="O59" t="n">
+      <c r="O59">
         <v>1657875982396.844</v>
       </c>
-      <c r="P59" t="n">
+      <c r="P59">
         <v>1696743761857.339</v>
       </c>
-      <c r="Q59" t="n">
+      <c r="Q59">
         <v>73281350166.97247</v>
       </c>
-      <c r="R59" t="n">
+      <c r="R59">
         <v>563767576205.6785</v>
       </c>
-      <c r="S59" t="n">
+      <c r="S59">
         <v>74128163031.37199</v>
       </c>
-      <c r="T59" t="n">
+      <c r="T59">
         <v>556434404263.7642</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="n">
+    <row r="60" spans="1:20">
+      <c r="A60" s="2">
         <v>41547</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>428170883508.7363</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C60">
         <v>2574154262564.814</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>451346970421.3373</v>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>2523145556371.246</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>1601783390897.538</v>
       </c>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>11674350623147.77</v>
       </c>
-      <c r="H60" t="n">
+      <c r="H60">
         <v>1624326588677.393</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>11609548769443.17</v>
       </c>
-      <c r="J60" t="n">
+      <c r="J60">
         <v>1099622174581.046</v>
       </c>
-      <c r="K60" t="n">
+      <c r="K60">
         <v>4007706669919.347</v>
       </c>
-      <c r="L60" t="n">
+      <c r="L60">
         <v>1108643937705.274</v>
       </c>
-      <c r="M60" t="n">
+      <c r="M60">
         <v>3982251592530.059</v>
       </c>
-      <c r="N60" t="n">
+      <c r="N60">
         <v>147338494919.8446</v>
       </c>
-      <c r="O60" t="n">
+      <c r="O60">
         <v>2220526155444.477</v>
       </c>
-      <c r="P60" t="n">
+      <c r="P60">
         <v>2137245367506.762</v>
       </c>
-      <c r="Q60" t="n">
+      <c r="Q60">
         <v>86143014694.35742</v>
       </c>
-      <c r="R60" t="n">
+      <c r="R60">
         <v>575946513334.5178</v>
       </c>
-      <c r="S60" t="n">
+      <c r="S60">
         <v>87425439640.66064</v>
       </c>
-      <c r="T60" t="n">
+      <c r="T60">
         <v>546041710391.3766</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="n">
+    <row r="61" spans="1:20">
+      <c r="A61" s="2">
         <v>41639</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>469130647042.6978</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C61">
         <v>2811923321154.888</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>460296567074.8207</v>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>2568341381860.844</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>1616240161986.659</v>
       </c>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>11843744980866.82</v>
       </c>
-      <c r="H61" t="n">
+      <c r="H61">
         <v>1628205766424.355</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>11919783421925.56</v>
       </c>
-      <c r="J61" t="n">
+      <c r="J61">
         <v>1191134369264.217</v>
       </c>
-      <c r="K61" t="n">
+      <c r="K61">
         <v>3938416059602.247</v>
       </c>
-      <c r="L61" t="n">
+      <c r="L61">
         <v>1165942298335.174</v>
       </c>
-      <c r="M61" t="n">
+      <c r="M61">
         <v>3883984864193.548</v>
       </c>
-      <c r="N61" t="n">
+      <c r="N61">
         <v>136580131050.98</v>
       </c>
-      <c r="O61" t="n">
+      <c r="O61">
         <v>2031065164450.939</v>
       </c>
-      <c r="P61" t="n">
+      <c r="P61">
         <v>2236429833502.013</v>
       </c>
-      <c r="Q61" t="n">
+      <c r="Q61">
         <v>81892398688.02676</v>
       </c>
-      <c r="R61" t="n">
+      <c r="R61">
         <v>601336972936.8885</v>
       </c>
-      <c r="S61" t="n">
+      <c r="S61">
         <v>83037210369.42366</v>
       </c>
-      <c r="T61" t="n">
+      <c r="T61">
         <v>560225871072.4265</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="n">
+    <row r="62" spans="1:20">
+      <c r="A62" s="2">
         <v>41729</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>462952668708.9851</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C62">
         <v>2333341300513.442</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>455882749201.5167</v>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>2600225848723.936</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>1695848935587.285</v>
       </c>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>12177019838918.99</v>
       </c>
-      <c r="H62" t="n">
+      <c r="H62">
         <v>1683420519632.778</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>12234000731776.01</v>
       </c>
-      <c r="J62" t="n">
+      <c r="J62">
         <v>1269679416518.381</v>
       </c>
-      <c r="K62" t="n">
+      <c r="K62">
         <v>3846518964835.681</v>
       </c>
-      <c r="L62" t="n">
+      <c r="L62">
         <v>1276558800362.196</v>
       </c>
-      <c r="M62" t="n">
+      <c r="M62">
         <v>3857524874197.516</v>
       </c>
-      <c r="N62" t="n">
+      <c r="N62">
         <v>147801312000.744</v>
       </c>
-      <c r="O62" t="n">
+      <c r="O62">
         <v>1985051750268.682</v>
       </c>
-      <c r="P62" t="n">
+      <c r="P62">
         <v>1843081548747.131</v>
       </c>
-      <c r="Q62" t="n">
+      <c r="Q62">
         <v>87294315004.51552</v>
       </c>
-      <c r="R62" t="n">
+      <c r="R62">
         <v>488605534491.6263</v>
       </c>
-      <c r="S62" t="n">
+      <c r="S62">
         <v>83966432153.60258</v>
       </c>
-      <c r="T62" t="n">
+      <c r="T62">
         <v>565109342090.9271</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="n">
+    <row r="63" spans="1:20">
+      <c r="A63" s="2">
         <v>41820</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>468958190591.4256</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C63">
         <v>2606255464332.718</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>462845688341.7913</v>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>2639990791647.09</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>1678195674254.111</v>
       </c>
-      <c r="G63" t="n">
+      <c r="G63">
         <v>12688456101794.6</v>
       </c>
-      <c r="H63" t="n">
+      <c r="H63">
         <v>1657651804013.061</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>12617342744649.91</v>
       </c>
-      <c r="J63" t="n">
+      <c r="J63">
         <v>1506465701537.412</v>
       </c>
-      <c r="K63" t="n">
+      <c r="K63">
         <v>3990058392986.343</v>
       </c>
-      <c r="L63" t="n">
+      <c r="L63">
         <v>1508132863929.301</v>
       </c>
-      <c r="M63" t="n">
+      <c r="M63">
         <v>4136472363885.512</v>
       </c>
-      <c r="N63" t="n">
+      <c r="N63">
         <v>224966110109.5286</v>
       </c>
-      <c r="O63" t="n">
+      <c r="O63">
         <v>1552606800975.417</v>
       </c>
-      <c r="P63" t="n">
+      <c r="P63">
         <v>1619951879599.217</v>
       </c>
-      <c r="Q63" t="n">
+      <c r="Q63">
         <v>79651598675.96942</v>
       </c>
-      <c r="R63" t="n">
+      <c r="R63">
         <v>574519910257.3903</v>
       </c>
-      <c r="S63" t="n">
+      <c r="S63">
         <v>80756805042.46419</v>
       </c>
-      <c r="T63" t="n">
+      <c r="T63">
         <v>571735025152.188</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="n">
+    <row r="64" spans="1:20">
+      <c r="A64" s="2">
         <v>41912</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>438707617062.2985</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C64">
         <v>2748167959017.946</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>458765190165.978</v>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>2695464499967.381</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>1624614652770.553</v>
       </c>
-      <c r="G64" t="n">
+      <c r="G64">
         <v>12971124504666.41</v>
       </c>
-      <c r="H64" t="n">
+      <c r="H64">
         <v>1645819882792.75</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64">
         <v>12913084450870.07</v>
       </c>
-      <c r="J64" t="n">
+      <c r="J64">
         <v>1513218193892.055</v>
       </c>
-      <c r="K64" t="n">
+      <c r="K64">
         <v>4784765951787.272</v>
       </c>
-      <c r="L64" t="n">
+      <c r="L64">
         <v>1529099269119.52</v>
       </c>
-      <c r="M64" t="n">
+      <c r="M64">
         <v>4696260042474.113</v>
       </c>
-      <c r="N64" t="n">
+      <c r="N64">
         <v>205614408735.6587</v>
       </c>
-      <c r="O64" t="n">
+      <c r="O64">
         <v>3112693167488.927</v>
       </c>
-      <c r="P64" t="n">
+      <c r="P64">
         <v>3013218453484.407</v>
       </c>
-      <c r="Q64" t="n">
+      <c r="Q64">
         <v>79712851127.17619</v>
       </c>
-      <c r="R64" t="n">
+      <c r="R64">
         <v>637253004572.9481</v>
       </c>
-      <c r="S64" t="n">
+      <c r="S64">
         <v>80804777833.32822</v>
       </c>
-      <c r="T64" t="n">
+      <c r="T64">
         <v>609655495187.2802</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="n">
+    <row r="65" spans="1:20">
+      <c r="A65" s="2">
         <v>42004</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>473612424523.8029</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C65">
         <v>2991955532760.071</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>466276150389.4014</v>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>2730522401496.224</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>1662768761658.443</v>
       </c>
-      <c r="G65" t="n">
+      <c r="G65">
         <v>13268256658518.81</v>
       </c>
-      <c r="H65" t="n">
+      <c r="H65">
         <v>1675297188038.933</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>13352447062392.13</v>
       </c>
-      <c r="J65" t="n">
+      <c r="J65">
         <v>1584372227871.338</v>
       </c>
-      <c r="K65" t="n">
+      <c r="K65">
         <v>6051946728251.131</v>
       </c>
-      <c r="L65" t="n">
+      <c r="L65">
         <v>1586991999567.057</v>
       </c>
-      <c r="M65" t="n">
+      <c r="M65">
         <v>6002553183250.536</v>
       </c>
-      <c r="N65" t="n">
+      <c r="N65">
         <v>183069842241.5837</v>
       </c>
-      <c r="O65" t="n">
+      <c r="O65">
         <v>5452485959185.351</v>
       </c>
-      <c r="P65" t="n">
+      <c r="P65">
         <v>5571246185643.12</v>
       </c>
-      <c r="Q65" t="n">
+      <c r="Q65">
         <v>78401049815.733</v>
       </c>
-      <c r="R65" t="n">
+      <c r="R65">
         <v>644082619773.9565</v>
       </c>
-      <c r="S65" t="n">
+      <c r="S65">
         <v>79161391715.82883</v>
       </c>
-      <c r="T65" t="n">
+      <c r="T65">
         <v>596326079654.4985</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="n">
+    <row r="66" spans="1:20">
+      <c r="A66" s="2">
         <v>42094</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>463539376371.714</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C66">
         <v>2477740850010.744</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>459325088072.6823</v>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>2764950915812.404</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>1690956585509.578</v>
       </c>
-      <c r="G66" t="n">
+      <c r="G66">
         <v>13806392521340</v>
       </c>
-      <c r="H66" t="n">
+      <c r="H66">
         <v>1677823780836.448</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>13854657995907.86</v>
       </c>
-      <c r="J66" t="n">
+      <c r="J66">
         <v>1630477405499.137</v>
       </c>
-      <c r="K66" t="n">
+      <c r="K66">
         <v>7666320537266.491</v>
       </c>
-      <c r="L66" t="n">
+      <c r="L66">
         <v>1621282177010.258</v>
       </c>
-      <c r="M66" t="n">
+      <c r="M66">
         <v>7662026682894.327</v>
       </c>
-      <c r="N66" t="n">
+      <c r="N66">
         <v>224979174981.5126</v>
       </c>
-      <c r="O66" t="n">
+      <c r="O66">
         <v>6637307218691.879</v>
       </c>
-      <c r="P66" t="n">
+      <c r="P66">
         <v>6514533682131.26</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="Q66">
         <v>70452986235.64055</v>
       </c>
-      <c r="R66" t="n">
+      <c r="R66">
         <v>506907350953.1747</v>
       </c>
-      <c r="S66" t="n">
+      <c r="S66">
         <v>67880167682.31677</v>
       </c>
-      <c r="T66" t="n">
+      <c r="T66">
         <v>584275462155.0862</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="n">
+    <row r="67" spans="1:20">
+      <c r="A67" s="2">
         <v>42185</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>484736709074.9323</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C67">
         <v>2771702428966.183</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>477133711076.4397</v>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>2806066160136.976</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>1708711033366.728</v>
       </c>
-      <c r="G67" t="n">
+      <c r="G67">
         <v>14318270465439.96</v>
       </c>
-      <c r="H67" t="n">
+      <c r="H67">
         <v>1691382803998.565</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>14237735060154.2</v>
       </c>
-      <c r="J67" t="n">
+      <c r="J67">
         <v>1600112016891.739</v>
       </c>
-      <c r="K67" t="n">
+      <c r="K67">
         <v>9426333694522.039</v>
       </c>
-      <c r="L67" t="n">
+      <c r="L67">
         <v>1590650563718.311</v>
       </c>
-      <c r="M67" t="n">
+      <c r="M67">
         <v>9605589902165.605</v>
       </c>
-      <c r="N67" t="n">
+      <c r="N67">
         <v>198130307752.9703</v>
       </c>
-      <c r="O67" t="n">
+      <c r="O67">
         <v>15833044400823.47</v>
       </c>
-      <c r="P67" t="n">
+      <c r="P67">
         <v>15980372018711.72</v>
       </c>
-      <c r="Q67" t="n">
+      <c r="Q67">
         <v>67076569648.77388</v>
       </c>
-      <c r="R67" t="n">
+      <c r="R67">
         <v>551005517817.993</v>
       </c>
-      <c r="S67" t="n">
+      <c r="S67">
         <v>68493123026.3959</v>
       </c>
-      <c r="T67" t="n">
+      <c r="T67">
         <v>551452386311.7627</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="n">
+    <row r="68" spans="1:20">
+      <c r="A68" s="2">
         <v>42277</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>476674666418.895</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C68">
         <v>2884161898732.313</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>494165614018.6757</v>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>2830635789113.002</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>1688324149014.42</v>
       </c>
-      <c r="G68" t="n">
+      <c r="G68">
         <v>14752969145515.56</v>
       </c>
-      <c r="H68" t="n">
+      <c r="H68">
         <v>1707623014020.666</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>14694703194091.34</v>
       </c>
-      <c r="J68" t="n">
+      <c r="J68">
         <v>1487419497556.899</v>
       </c>
-      <c r="K68" t="n">
+      <c r="K68">
         <v>6717720866933.391</v>
       </c>
-      <c r="L68" t="n">
+      <c r="L68">
         <v>1501436407742.424</v>
       </c>
-      <c r="M68" t="n">
+      <c r="M68">
         <v>6584176044923.458</v>
       </c>
-      <c r="N68" t="n">
+      <c r="N68">
         <v>204023682921.5618</v>
       </c>
-      <c r="O68" t="n">
+      <c r="O68">
         <v>9659468254954.008</v>
       </c>
-      <c r="P68" t="n">
+      <c r="P68">
         <v>9530189326896.615</v>
       </c>
-      <c r="Q68" t="n">
+      <c r="Q68">
         <v>66817991870.8185</v>
       </c>
-      <c r="R68" t="n">
+      <c r="R68">
         <v>599516219796.7217</v>
       </c>
-      <c r="S68" t="n">
+      <c r="S68">
         <v>67622896132.4373</v>
       </c>
-      <c r="T68" t="n">
+      <c r="T68">
         <v>573834879439.7896</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="n">
+    <row r="69" spans="1:20">
+      <c r="A69" s="2">
         <v>42369</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>484881506940.7614</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C69">
         <v>3143816804643.102</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>479024018532.5074</v>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>2863930622086.597</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>1711553262768.642</v>
       </c>
-      <c r="G69" t="n">
+      <c r="G69">
         <v>15044445315288.18</v>
       </c>
-      <c r="H69" t="n">
+      <c r="H69">
         <v>1724381129411.942</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69">
         <v>15140342143997.07</v>
       </c>
-      <c r="J69" t="n">
+      <c r="J69">
         <v>1518755948876.193</v>
       </c>
-      <c r="K69" t="n">
+      <c r="K69">
         <v>8507541551810.716</v>
       </c>
-      <c r="L69" t="n">
+      <c r="L69">
         <v>1544531039618.365</v>
       </c>
-      <c r="M69" t="n">
+      <c r="M69">
         <v>8455585893026.359</v>
       </c>
-      <c r="N69" t="n">
+      <c r="N69">
         <v>172083223613.7685</v>
       </c>
-      <c r="O69" t="n">
+      <c r="O69">
         <v>8921224618350.668</v>
       </c>
-      <c r="P69" t="n">
+      <c r="P69">
         <v>8948452833058.172</v>
       </c>
-      <c r="Q69" t="n">
+      <c r="Q69">
         <v>63454430225.33417</v>
       </c>
-      <c r="R69" t="n">
+      <c r="R69">
         <v>626926811141.1642</v>
       </c>
-      <c r="S69" t="n">
+      <c r="S69">
         <v>63769123536.63903</v>
       </c>
-      <c r="T69" t="n">
+      <c r="T69">
         <v>574150759912.076</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="n">
+    <row r="70" spans="1:20">
+      <c r="A70" s="2">
         <v>42460</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>487347240318.4093</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C70">
         <v>2608749627551.574</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>485090599813.6146</v>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>2913960956621.127</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>1762691717449.568</v>
       </c>
-      <c r="G70" t="n">
+      <c r="G70">
         <v>15514003294092.61</v>
       </c>
-      <c r="H70" t="n">
+      <c r="H70">
         <v>1745234140944.417</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>15564253699539.33</v>
       </c>
-      <c r="J70" t="n">
+      <c r="J70">
         <v>1440794865403.569</v>
       </c>
-      <c r="K70" t="n">
+      <c r="K70">
         <v>7148625810770.326</v>
       </c>
-      <c r="L70" t="n">
+      <c r="L70">
         <v>1417904318780.178</v>
       </c>
-      <c r="M70" t="n">
+      <c r="M70">
         <v>7129306805290.157</v>
       </c>
-      <c r="N70" t="n">
+      <c r="N70">
         <v>186347779945.5195</v>
       </c>
-      <c r="O70" t="n">
+      <c r="O70">
         <v>5054903930241.347</v>
       </c>
-      <c r="P70" t="n">
+      <c r="P70">
         <v>4911652941312.721</v>
       </c>
-      <c r="Q70" t="n">
+      <c r="Q70">
         <v>66657999633.71339</v>
       </c>
-      <c r="R70" t="n">
+      <c r="R70">
         <v>477969517481.054</v>
       </c>
-      <c r="S70" t="n">
+      <c r="S70">
         <v>64567772674.12003</v>
       </c>
-      <c r="T70" t="n">
+      <c r="T70">
         <v>555857232296.327</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="n">
+    <row r="71" spans="1:20">
+      <c r="A71" s="2">
         <v>42551</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>505090105782.6243</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C71">
         <v>2921566116202.304</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>497120407863.3401</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>2955178384401.613</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>1781376201004.29</v>
       </c>
-      <c r="G71" t="n">
+      <c r="G71">
         <v>16026721879705.97</v>
       </c>
-      <c r="H71" t="n">
+      <c r="H71">
         <v>1768100121893.078</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>15931949924217.14</v>
       </c>
-      <c r="J71" t="n">
+      <c r="J71">
         <v>1527888088510.219</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71">
         <v>7310469236058.995</v>
       </c>
-      <c r="L71" t="n">
+      <c r="L71">
         <v>1508872083782.859</v>
       </c>
-      <c r="M71" t="n">
+      <c r="M71">
         <v>7520363094050.764</v>
       </c>
-      <c r="N71" t="n">
+      <c r="N71">
         <v>184187948725.7995</v>
       </c>
-      <c r="O71" t="n">
+      <c r="O71">
         <v>5061991917311.282</v>
       </c>
-      <c r="P71" t="n">
+      <c r="P71">
         <v>5236424835733.993</v>
       </c>
-      <c r="Q71" t="n">
+      <c r="Q71">
         <v>65518398447.88487</v>
       </c>
-      <c r="R71" t="n">
+      <c r="R71">
         <v>551112494914.0216</v>
       </c>
-      <c r="S71" t="n">
+      <c r="S71">
         <v>66563588251.13235</v>
       </c>
-      <c r="T71" t="n">
+      <c r="T71">
         <v>553176270391.7025</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="n">
+    <row r="72" spans="1:20">
+      <c r="A72" s="2">
         <v>42643</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>501672734917.802</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C72">
         <v>3069841249989.431</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>516483420689.7715</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>3017350143489.095</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>1815662883268.408</v>
       </c>
-      <c r="G72" t="n">
+      <c r="G72">
         <v>16404070272144.52</v>
       </c>
-      <c r="H72" t="n">
+      <c r="H72">
         <v>1833373954817.573</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>16344583552526.79</v>
       </c>
-      <c r="J72" t="n">
+      <c r="J72">
         <v>1621316674938.706</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72">
         <v>7641733049224.995</v>
       </c>
-      <c r="L72" t="n">
+      <c r="L72">
         <v>1637080773441.047</v>
       </c>
-      <c r="M72" t="n">
+      <c r="M72">
         <v>7486557276325.458</v>
       </c>
-      <c r="N72" t="n">
+      <c r="N72">
         <v>225813048237.4553</v>
       </c>
-      <c r="O72" t="n">
+      <c r="O72">
         <v>5084174305460.531</v>
       </c>
-      <c r="P72" t="n">
+      <c r="P72">
         <v>5066675055848.149</v>
       </c>
-      <c r="Q72" t="n">
+      <c r="Q72">
         <v>64760163154.21049</v>
       </c>
-      <c r="R72" t="n">
+      <c r="R72">
         <v>585838685109.3893</v>
       </c>
-      <c r="S72" t="n">
+      <c r="S72">
         <v>65498335860.2038</v>
       </c>
-      <c r="T72" t="n">
+      <c r="T72">
         <v>559982053775.629</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="n">
+    <row r="73" spans="1:20">
+      <c r="A73" s="2">
         <v>42735</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>521145387482.1611</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C73">
         <v>3379568089736.906</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>516491008952.233</v>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>3081375921694.046</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>1818290924236.582</v>
       </c>
-      <c r="G73" t="n">
+      <c r="G73">
         <v>16708979027980.59</v>
       </c>
-      <c r="H73" t="n">
+      <c r="H73">
         <v>1834799899991.336</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>16810490804867.82</v>
       </c>
-      <c r="J73" t="n">
+      <c r="J73">
         <v>1564757638488.412</v>
       </c>
-      <c r="K73" t="n">
+      <c r="K73">
         <v>7957405297043.761</v>
       </c>
-      <c r="L73" t="n">
+      <c r="L73">
         <v>1593203979407.25</v>
       </c>
-      <c r="M73" t="n">
+      <c r="M73">
         <v>7917049609030.817</v>
       </c>
-      <c r="N73" t="n">
+      <c r="N73">
         <v>203278737796.1949</v>
       </c>
-      <c r="O73" t="n">
+      <c r="O73">
         <v>4911433812178.982</v>
       </c>
-      <c r="P73" t="n">
+      <c r="P73">
         <v>4833413308223.994</v>
       </c>
-      <c r="Q73" t="n">
+      <c r="Q73">
         <v>67014547773.83379</v>
       </c>
-      <c r="R73" t="n">
+      <c r="R73">
         <v>622667105029.4948</v>
       </c>
-      <c r="S73" t="n">
+      <c r="S73">
         <v>67143491463.70131</v>
       </c>
-      <c r="T73" t="n">
+      <c r="T73">
         <v>565680646567.5179</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="n">
+    <row r="74" spans="1:20">
+      <c r="A74" s="2">
         <v>42825</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>534833424242.672</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C74">
         <v>2874963734754.743</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>533896710389.9794</v>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>3197666093846.463</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>1919005402000.494</v>
       </c>
-      <c r="G74" t="n">
+      <c r="G74">
         <v>17197172430624.6</v>
       </c>
-      <c r="H74" t="n">
+      <c r="H74">
         <v>1895133042982.636</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>17266899932688.2</v>
       </c>
-      <c r="J74" t="n">
+      <c r="J74">
         <v>1805519109154.942</v>
       </c>
-      <c r="K74" t="n">
+      <c r="K74">
         <v>8372966542145.253</v>
       </c>
-      <c r="L74" t="n">
+      <c r="L74">
         <v>1772563770404.337</v>
       </c>
-      <c r="M74" t="n">
+      <c r="M74">
         <v>8304914770467.554</v>
       </c>
-      <c r="N74" t="n">
+      <c r="N74">
         <v>274471244933.9617</v>
       </c>
-      <c r="O74" t="n">
+      <c r="O74">
         <v>4117385934593.786</v>
       </c>
-      <c r="P74" t="n">
+      <c r="P74">
         <v>3919451681755.065</v>
       </c>
-      <c r="Q74" t="n">
+      <c r="Q74">
         <v>75920510968.37007</v>
       </c>
-      <c r="R74" t="n">
+      <c r="R74">
         <v>516971618268.0336</v>
       </c>
-      <c r="S74" t="n">
+      <c r="S74">
         <v>74331248828.5493</v>
       </c>
-      <c r="T74" t="n">
+      <c r="T74">
         <v>596004038780.8243</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="n">
+    <row r="75" spans="1:20">
+      <c r="A75" s="2">
         <v>42916</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>542826038381.4483</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C75">
         <v>3199628176993.644</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>535080036179.5141</v>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>3232901758820.306</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>1904063329334.061</v>
       </c>
-      <c r="G75" t="n">
+      <c r="G75">
         <v>17824471437055.96</v>
       </c>
-      <c r="H75" t="n">
+      <c r="H75">
         <v>1895770741948.024</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75">
         <v>17713355336055.31</v>
       </c>
-      <c r="J75" t="n">
+      <c r="J75">
         <v>1844326381662.439</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75">
         <v>8312672701380.889</v>
       </c>
-      <c r="L75" t="n">
+      <c r="L75">
         <v>1826492679819.124</v>
       </c>
-      <c r="M75" t="n">
+      <c r="M75">
         <v>8535117685940.306</v>
       </c>
-      <c r="N75" t="n">
+      <c r="N75">
         <v>262022536373.6331</v>
       </c>
-      <c r="O75" t="n">
+      <c r="O75">
         <v>4029633891709.773</v>
       </c>
-      <c r="P75" t="n">
+      <c r="P75">
         <v>4259272095349.866</v>
       </c>
-      <c r="Q75" t="n">
+      <c r="Q75">
         <v>67515156299.90826</v>
       </c>
-      <c r="R75" t="n">
+      <c r="R75">
         <v>605939318280.7109</v>
       </c>
-      <c r="S75" t="n">
+      <c r="S75">
         <v>68022755986.88067</v>
       </c>
-      <c r="T75" t="n">
+      <c r="T75">
         <v>610910913554.7772</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="n">
+    <row r="76" spans="1:20">
+      <c r="A76" s="2">
         <v>43008</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>539605575031.696</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C76">
         <v>3361299583441.992</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>551214462623.8895</v>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>3313013484178.195</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>1898357207558.455</v>
       </c>
-      <c r="G76" t="n">
+      <c r="G76">
         <v>18261720541202.17</v>
       </c>
-      <c r="H76" t="n">
+      <c r="H76">
         <v>1913551296971.643</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>18204488750980.72</v>
       </c>
-      <c r="J76" t="n">
+      <c r="J76">
         <v>1884766354696.176</v>
       </c>
-      <c r="K76" t="n">
+      <c r="K76">
         <v>8828346996447.035</v>
       </c>
-      <c r="L76" t="n">
+      <c r="L76">
         <v>1910886752353.221</v>
       </c>
-      <c r="M76" t="n">
+      <c r="M76">
         <v>8636813396000.375</v>
       </c>
-      <c r="N76" t="n">
+      <c r="N76">
         <v>276817216429.8729</v>
       </c>
-      <c r="O76" t="n">
+      <c r="O76">
         <v>5134842150106.052</v>
       </c>
-      <c r="P76" t="n">
+      <c r="P76">
         <v>5272390852573.814</v>
       </c>
-      <c r="Q76" t="n">
+      <c r="Q76">
         <v>68230262310.72099</v>
       </c>
-      <c r="R76" t="n">
+      <c r="R76">
         <v>611430559523.5186</v>
       </c>
-      <c r="S76" t="n">
+      <c r="S76">
         <v>69236947915.77409</v>
       </c>
-      <c r="T76" t="n">
+      <c r="T76">
         <v>584457230725.4054</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="n">
+    <row r="77" spans="1:20">
+      <c r="A77" s="2">
         <v>43100</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>566766721393.2771</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C77">
         <v>3689595971868.512</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>563159185535.0533</v>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>3372056956680.467</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>1887295945271.396</v>
       </c>
-      <c r="G77" t="n">
+      <c r="G77">
         <v>18492358676920.05</v>
       </c>
-      <c r="H77" t="n">
+      <c r="H77">
         <v>1908134838141.661</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>18599056994234.62</v>
       </c>
-      <c r="J77" t="n">
+      <c r="J77">
         <v>2109351241136.365</v>
       </c>
-      <c r="K77" t="n">
+      <c r="K77">
         <v>8729356430989.049</v>
       </c>
-      <c r="L77" t="n">
+      <c r="L77">
         <v>2133983305436.875</v>
       </c>
-      <c r="M77" t="n">
+      <c r="M77">
         <v>8735826702072.343</v>
       </c>
-      <c r="N77" t="n">
+      <c r="N77">
         <v>312812797256.0707</v>
       </c>
-      <c r="O77" t="n">
+      <c r="O77">
         <v>4194763379452.695</v>
       </c>
-      <c r="P77" t="n">
+      <c r="P77">
         <v>4025361775128.264</v>
       </c>
-      <c r="Q77" t="n">
+      <c r="Q77">
         <v>70755013435.55705</v>
       </c>
-      <c r="R77" t="n">
+      <c r="R77">
         <v>649473079087.4926</v>
       </c>
-      <c r="S77" t="n">
+      <c r="S77">
         <v>71008490708.69633</v>
       </c>
-      <c r="T77" t="n">
+      <c r="T77">
         <v>592018331194.8223</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="n">
+    <row r="78" spans="1:20">
+      <c r="A78" s="2">
         <v>43190</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>571953553307.9951</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C78">
         <v>3125994595100.317</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>570720764825.374</v>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>3465281657801.96</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>1984735675650.292</v>
       </c>
-      <c r="G78" t="n">
+      <c r="G78">
         <v>18989993739335.33</v>
       </c>
-      <c r="H78" t="n">
+      <c r="H78">
         <v>1953124837870.707</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78">
         <v>19064285691938.75</v>
       </c>
-      <c r="J78" t="n">
+      <c r="J78">
         <v>2014834074754.295</v>
       </c>
-      <c r="K78" t="n">
+      <c r="K78">
         <v>8501468097349.11</v>
       </c>
-      <c r="L78" t="n">
+      <c r="L78">
         <v>1974633462265.302</v>
       </c>
-      <c r="M78" t="n">
+      <c r="M78">
         <v>8404195253002.857</v>
       </c>
-      <c r="N78" t="n">
+      <c r="N78">
         <v>326509444736.1756</v>
       </c>
-      <c r="O78" t="n">
+      <c r="O78">
         <v>4299730787794.59</v>
       </c>
-      <c r="P78" t="n">
+      <c r="P78">
         <v>4029563705320.829</v>
       </c>
-      <c r="Q78" t="n">
+      <c r="Q78">
         <v>73594282611.12384</v>
       </c>
-      <c r="R78" t="n">
+      <c r="R78">
         <v>527668297659.5451</v>
       </c>
-      <c r="S78" t="n">
+      <c r="S78">
         <v>72025030782.23274</v>
       </c>
-      <c r="T78" t="n">
+      <c r="T78">
         <v>607243851662.5846</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="n">
+    <row r="79" spans="1:20">
+      <c r="A79" s="2">
         <v>43281</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>587922921055.5862</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C79">
         <v>3488041249698.666</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>579950058169.2336</v>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>3521754742370.109</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>2010518522592.647</v>
       </c>
-      <c r="G79" t="n">
+      <c r="G79">
         <v>19754766769139.93</v>
       </c>
-      <c r="H79" t="n">
+      <c r="H79">
         <v>2006421149052.455</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>19625963947074.88</v>
       </c>
-      <c r="J79" t="n">
+      <c r="J79">
         <v>2040413427221.053</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K79">
         <v>7712298894032.484</v>
       </c>
-      <c r="L79" t="n">
+      <c r="L79">
         <v>2016955521682.437</v>
       </c>
-      <c r="M79" t="n">
+      <c r="M79">
         <v>7960681038638.463</v>
       </c>
-      <c r="N79" t="n">
+      <c r="N79">
         <v>298427841852.0201</v>
       </c>
-      <c r="O79" t="n">
+      <c r="O79">
         <v>3709451960345.007</v>
       </c>
-      <c r="P79" t="n">
+      <c r="P79">
         <v>4024420737918.819</v>
       </c>
-      <c r="Q79" t="n">
+      <c r="Q79">
         <v>77455117582.16858</v>
       </c>
-      <c r="R79" t="n">
+      <c r="R79">
         <v>614496515196.7841</v>
       </c>
-      <c r="S79" t="n">
+      <c r="S79">
         <v>77602245063.96957</v>
       </c>
-      <c r="T79" t="n">
+      <c r="T79">
         <v>620201420408.7151</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="n">
+    <row r="80" spans="1:20">
+      <c r="A80" s="2">
         <v>43373</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>570104930131.6154</v>
       </c>
-      <c r="C80" t="n">
+      <c r="C80">
         <v>3620346143655.488</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>581590170987.3363</v>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>3576577720441.393</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>1986468910335.331</v>
       </c>
-      <c r="G80" t="n">
+      <c r="G80">
         <v>20204210937503.41</v>
       </c>
-      <c r="H80" t="n">
+      <c r="H80">
         <v>2000200984426.775</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80">
         <v>20154641042945.47</v>
       </c>
-      <c r="J80" t="n">
+      <c r="J80">
         <v>1960007358469.833</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K80">
         <v>7377474739299.367</v>
       </c>
-      <c r="L80" t="n">
+      <c r="L80">
         <v>2004317605236.006</v>
       </c>
-      <c r="M80" t="n">
+      <c r="M80">
         <v>7136595667394.443</v>
       </c>
-      <c r="N80" t="n">
+      <c r="N80">
         <v>302823061365.4902</v>
       </c>
-      <c r="O80" t="n">
+      <c r="O80">
         <v>2934308839399.756</v>
       </c>
-      <c r="P80" t="n">
+      <c r="P80">
         <v>3347656971522.787</v>
       </c>
-      <c r="Q80" t="n">
+      <c r="Q80">
         <v>77379798504.93045</v>
       </c>
-      <c r="R80" t="n">
+      <c r="R80">
         <v>681030620045.8417</v>
       </c>
-      <c r="S80" t="n">
+      <c r="S80">
         <v>78714577037.80173</v>
       </c>
-      <c r="T80" t="n">
+      <c r="T80">
         <v>653508375684.1189</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
+    <row r="81" spans="1:20">
+      <c r="A81" s="2">
         <v>43465</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>592971699453.3215</v>
       </c>
-      <c r="C81" t="n">
+      <c r="C81">
         <v>3968903135418.746</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>589809648170.6947</v>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>3626006207369.484</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>2018913377606.876</v>
       </c>
-      <c r="G81" t="n">
+      <c r="G81">
         <v>20534364416412.15</v>
       </c>
-      <c r="H81" t="n">
+      <c r="H81">
         <v>2042317768507.189</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81">
         <v>20661041009341.74</v>
       </c>
-      <c r="J81" t="n">
+      <c r="J81">
         <v>1954388991772.059</v>
       </c>
-      <c r="K81" t="n">
+      <c r="K81">
         <v>6552536387149.854</v>
       </c>
-      <c r="L81" t="n">
+      <c r="L81">
         <v>1962496486862.889</v>
       </c>
-      <c r="M81" t="n">
+      <c r="M81">
         <v>6668171492669.151</v>
       </c>
-      <c r="N81" t="n">
+      <c r="N81">
         <v>286011538311.118</v>
       </c>
-      <c r="O81" t="n">
+      <c r="O81">
         <v>2769485173148.021</v>
       </c>
-      <c r="P81" t="n">
+      <c r="P81">
         <v>2247582086218.177</v>
       </c>
-      <c r="Q81" t="n">
+      <c r="Q81">
         <v>78456968821.84993</v>
       </c>
-      <c r="R81" t="n">
+      <c r="R81">
         <v>694422291983.4513</v>
       </c>
-      <c r="S81" t="n">
+      <c r="S81">
         <v>79045809705.71085</v>
       </c>
-      <c r="T81" t="n">
+      <c r="T81">
         <v>639761670503.2458</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="n">
+    <row r="82" spans="1:20">
+      <c r="A82" s="2">
         <v>43555</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>582849307539.2555</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C82">
         <v>3304369575054.153</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>581260076074.3005</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>3658829059766.154</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>2074126861694.213</v>
       </c>
-      <c r="G82" t="n">
+      <c r="G82">
         <v>21203956534562.07</v>
       </c>
-      <c r="H82" t="n">
+      <c r="H82">
         <v>2034893980282.661</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82">
         <v>21257965384070.2</v>
       </c>
-      <c r="J82" t="n">
+      <c r="J82">
         <v>1999114669246.353</v>
       </c>
-      <c r="K82" t="n">
+      <c r="K82">
         <v>8398515262151.995</v>
       </c>
-      <c r="L82" t="n">
+      <c r="L82">
         <v>1943364412633.83</v>
       </c>
-      <c r="M82" t="n">
+      <c r="M82">
         <v>8338801853466.139</v>
       </c>
-      <c r="N82" t="n">
+      <c r="N82">
         <v>288285234978.6492</v>
       </c>
-      <c r="O82" t="n">
+      <c r="O82">
         <v>5088661914895.681</v>
       </c>
-      <c r="P82" t="n">
+      <c r="P82">
         <v>4793012743784.236</v>
       </c>
-      <c r="Q82" t="n">
+      <c r="Q82">
         <v>80196812119.32758</v>
       </c>
-      <c r="R82" t="n">
+      <c r="R82">
         <v>555178619664.16</v>
       </c>
-      <c r="S82" t="n">
+      <c r="S82">
         <v>78282982970.93752</v>
       </c>
-      <c r="T82" t="n">
+      <c r="T82">
         <v>633195124025.7574</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="n">
+    <row r="83" spans="1:20">
+      <c r="A83" s="2">
         <v>43646</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>591215469691.5051</v>
       </c>
-      <c r="C83" t="n">
+      <c r="C83">
         <v>3667838940356.82</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>583392699313.239</v>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>3699977823312.47</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>2042645700371.292</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G83">
         <v>21746733832855.69</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H83">
         <v>2042193869144.483</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83">
         <v>21595196701786.21</v>
       </c>
-      <c r="J83" t="n">
+      <c r="J83">
         <v>1972300649393.317</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K83">
         <v>7989837199087.91</v>
       </c>
-      <c r="L83" t="n">
+      <c r="L83">
         <v>1975664898065.6</v>
       </c>
-      <c r="M83" t="n">
+      <c r="M83">
         <v>8206512251162.657</v>
       </c>
-      <c r="N83" t="n">
+      <c r="N83">
         <v>281500201253.6539</v>
       </c>
-      <c r="O83" t="n">
+      <c r="O83">
         <v>5286429861153.91</v>
       </c>
-      <c r="P83" t="n">
+      <c r="P83">
         <v>5651379826047.426</v>
       </c>
-      <c r="Q83" t="n">
+      <c r="Q83">
         <v>73044975606.65781</v>
       </c>
-      <c r="R83" t="n">
+      <c r="R83">
         <v>631322418371.2908</v>
       </c>
-      <c r="S83" t="n">
+      <c r="S83">
         <v>72950735760.20038</v>
       </c>
-      <c r="T83" t="n">
+      <c r="T83">
         <v>635025652122.0052</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="n">
+    <row r="84" spans="1:20">
+      <c r="A84" s="2">
         <v>43738</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>569420337502.9211</v>
       </c>
-      <c r="C84" t="n">
+      <c r="C84">
         <v>3773429273517.912</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>583209463838.0366</v>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>3733119825013.371</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>2046371082353.684</v>
       </c>
-      <c r="G84" t="n">
+      <c r="G84">
         <v>22096842067738.71</v>
       </c>
-      <c r="H84" t="n">
+      <c r="H84">
         <v>2062560131509.989</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84">
         <v>22059458776559.73</v>
       </c>
-      <c r="J84" t="n">
+      <c r="J84">
         <v>1872289549939.181</v>
       </c>
-      <c r="K84" t="n">
+      <c r="K84">
         <v>8044872350667.11</v>
       </c>
-      <c r="L84" t="n">
+      <c r="L84">
         <v>1941795449900.433</v>
       </c>
-      <c r="M84" t="n">
+      <c r="M84">
         <v>7740076293019.557</v>
       </c>
-      <c r="N84" t="n">
+      <c r="N84">
         <v>283997624591.9379</v>
       </c>
-      <c r="O84" t="n">
+      <c r="O84">
         <v>4477256308886.158</v>
       </c>
-      <c r="P84" t="n">
+      <c r="P84">
         <v>5183089033883.078</v>
       </c>
-      <c r="Q84" t="n">
+      <c r="Q84">
         <v>70089929451.86032</v>
       </c>
-      <c r="R84" t="n">
+      <c r="R84">
         <v>676902693392.6389</v>
       </c>
-      <c r="S84" t="n">
+      <c r="S84">
         <v>71444036883.3893</v>
       </c>
-      <c r="T84" t="n">
+      <c r="T84">
         <v>648896127337.5524</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="n">
+    <row r="85" spans="1:20">
+      <c r="A85" s="2">
         <v>43830</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>579907300673.1858</v>
       </c>
-      <c r="C85" t="n">
+      <c r="C85">
         <v>4079367660596.928</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>577179406236.0386</v>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>3705110032139.227</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>2039627897857.323</v>
       </c>
-      <c r="G85" t="n">
+      <c r="G85">
         <v>22133180297722.41</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H85">
         <v>2066006678230.424</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85">
         <v>22285456873664.16</v>
       </c>
-      <c r="J85" t="n">
+      <c r="J85">
         <v>1934405665285.932</v>
       </c>
-      <c r="K85" t="n">
+      <c r="K85">
         <v>8571176862042.08</v>
       </c>
-      <c r="L85" t="n">
+      <c r="L85">
         <v>1897690932699.323</v>
       </c>
-      <c r="M85" t="n">
+      <c r="M85">
         <v>8742209666567.44</v>
       </c>
-      <c r="N85" t="n">
+      <c r="N85">
         <v>303142738035.4151</v>
       </c>
-      <c r="O85" t="n">
+      <c r="O85">
         <v>3975471427483.258</v>
       </c>
-      <c r="P85" t="n">
+      <c r="P85">
         <v>3182606553604.084</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="Q85">
         <v>70027379208.92941</v>
       </c>
-      <c r="R85" t="n">
+      <c r="R85">
         <v>684366856493.8051</v>
       </c>
-      <c r="S85" t="n">
+      <c r="S85">
         <v>71153161247.52534</v>
       </c>
-      <c r="T85" t="n">
+      <c r="T85">
         <v>631835618624.3816</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
+    <row r="86" spans="1:20">
+      <c r="A86" s="2">
         <v>43921</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>582298390718.1754</v>
       </c>
-      <c r="C86" t="n">
+      <c r="C86">
         <v>2980808719573.404</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>577537255310.5717</v>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>3346603008754.99</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>2094351710802.92</v>
       </c>
-      <c r="G86" t="n">
+      <c r="G86">
         <v>22776250596818.32</v>
       </c>
-      <c r="H86" t="n">
+      <c r="H86">
         <v>2047406829990.587</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86">
         <v>22810661286658</v>
       </c>
-      <c r="J86" t="n">
+      <c r="J86">
         <v>1409993046659.072</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86">
         <v>8001861178163.808</v>
       </c>
-      <c r="L86" t="n">
+      <c r="L86">
         <v>1340787034062.937</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M86">
         <v>8000809424790.47</v>
       </c>
-      <c r="N86" t="n">
+      <c r="N86">
         <v>346139629949.0309</v>
       </c>
-      <c r="O86" t="n">
+      <c r="O86">
         <v>7108515499947.218</v>
       </c>
-      <c r="P86" t="n">
+      <c r="P86">
         <v>6897233467135.291</v>
       </c>
-      <c r="Q86" t="n">
+      <c r="Q86">
         <v>67399238782.88826</v>
       </c>
-      <c r="R86" t="n">
+      <c r="R86">
         <v>472905321009.4617</v>
       </c>
-      <c r="S86" t="n">
+      <c r="S86">
         <v>64759778900.41386</v>
       </c>
-      <c r="T86" t="n">
+      <c r="T86">
         <v>548692491064.7771</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
+    <row r="87" spans="1:20">
+      <c r="A87" s="2">
         <v>44012</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>455532508274.3514</v>
       </c>
-      <c r="C87" t="n">
+      <c r="C87">
         <v>3675887638472.071</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>448934848380.3881</v>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>3717662612789.065</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>2149559065623.075</v>
       </c>
-      <c r="G87" t="n">
+      <c r="G87">
         <v>23959602126634.11</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H87">
         <v>2151784134129.609</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87">
         <v>23778494156679.01</v>
       </c>
-      <c r="J87" t="n">
+      <c r="J87">
         <v>1716701471448.922</v>
       </c>
-      <c r="K87" t="n">
+      <c r="K87">
         <v>9409436885925.021</v>
       </c>
-      <c r="L87" t="n">
+      <c r="L87">
         <v>1793903619770.011</v>
       </c>
-      <c r="M87" t="n">
+      <c r="M87">
         <v>9497172392239.236</v>
       </c>
-      <c r="N87" t="n">
+      <c r="N87">
         <v>426732447157.0718</v>
       </c>
-      <c r="O87" t="n">
+      <c r="O87">
         <v>5649863432544.797</v>
       </c>
-      <c r="P87" t="n">
+      <c r="P87">
         <v>6051061639726.123</v>
       </c>
-      <c r="Q87" t="n">
+      <c r="Q87">
         <v>48115417688.67715</v>
       </c>
-      <c r="R87" t="n">
+      <c r="R87">
         <v>638176950912.6383</v>
       </c>
-      <c r="S87" t="n">
+      <c r="S87">
         <v>47894418463.74801</v>
       </c>
-      <c r="T87" t="n">
+      <c r="T87">
         <v>639944721209.1166</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
+    <row r="88" spans="1:20">
+      <c r="A88" s="2">
         <v>44104</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>519438748474.5693</v>
       </c>
-      <c r="C88" t="n">
+      <c r="C88">
         <v>3901691987159.698</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>535337235670.7006</v>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>3863852135741.023</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>2101168784659.49</v>
       </c>
-      <c r="G88" t="n">
+      <c r="G88">
         <v>24482812135701.52</v>
       </c>
-      <c r="H88" t="n">
+      <c r="H88">
         <v>2122016195611.119</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88">
         <v>24465015052525.45</v>
       </c>
-      <c r="J88" t="n">
+      <c r="J88">
         <v>1871426750222.208</v>
       </c>
-      <c r="K88" t="n">
+      <c r="K88">
         <v>10432362284492.83</v>
       </c>
-      <c r="L88" t="n">
+      <c r="L88">
         <v>1956236534864.261</v>
       </c>
-      <c r="M88" t="n">
+      <c r="M88">
         <v>10132800505581.43</v>
       </c>
-      <c r="N88" t="n">
+      <c r="N88">
         <v>491595378083.5856</v>
       </c>
-      <c r="O88" t="n">
+      <c r="O88">
         <v>10043711630805.56</v>
       </c>
-      <c r="P88" t="n">
+      <c r="P88">
         <v>10755929130066.66</v>
       </c>
-      <c r="Q88" t="n">
+      <c r="Q88">
         <v>66462170968.14535</v>
       </c>
-      <c r="R88" t="n">
+      <c r="R88">
         <v>712371662987.6583</v>
       </c>
-      <c r="S88" t="n">
+      <c r="S88">
         <v>67901888458.53932</v>
       </c>
-      <c r="T88" t="n">
+      <c r="T88">
         <v>687147508546.597</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
+    <row r="89" spans="1:20">
+      <c r="A89" s="2">
         <v>44196</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>589123489306.5999</v>
       </c>
-      <c r="C89" t="n">
+      <c r="C89">
         <v>4357968536926.691</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>586800344977.1587</v>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>3986086105105.603</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>2108677377790.88</v>
       </c>
-      <c r="G89" t="n">
+      <c r="G89">
         <v>24941281960576.24</v>
       </c>
-      <c r="H89" t="n">
+      <c r="H89">
         <v>2136241367268.872</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89">
         <v>25121471614475.71</v>
       </c>
-      <c r="J89" t="n">
+      <c r="J89">
         <v>2228215656112.023</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K89">
         <v>11510676516329.15</v>
       </c>
-      <c r="L89" t="n">
+      <c r="L89">
         <v>2116607945061.503</v>
       </c>
-      <c r="M89" t="n">
+      <c r="M89">
         <v>11746279126356.57</v>
       </c>
-      <c r="N89" t="n">
+      <c r="N89">
         <v>476474565198.8699</v>
       </c>
-      <c r="O89" t="n">
+      <c r="O89">
         <v>6986374975068.354</v>
       </c>
-      <c r="P89" t="n">
+      <c r="P89">
         <v>5940179029664.275</v>
       </c>
-      <c r="Q89" t="n">
+      <c r="Q89">
         <v>66201394867.88194</v>
       </c>
-      <c r="R89" t="n">
+      <c r="R89">
         <v>751668328447.2726</v>
       </c>
-      <c r="S89" t="n">
+      <c r="S89">
         <v>68114258833.79616</v>
       </c>
-      <c r="T89" t="n">
+      <c r="T89">
         <v>700539716180.2994</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
+    <row r="90" spans="1:20">
+      <c r="A90" s="2">
         <v>44286</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>623132079652.2323</v>
       </c>
-      <c r="C90" t="n">
+      <c r="C90">
         <v>3629969543215.208</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>613650649231.4928</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>4000759048489.458</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>2203103969165.111</v>
       </c>
-      <c r="G90" t="n">
+      <c r="G90">
         <v>25676566974753.42</v>
       </c>
-      <c r="H90" t="n">
+      <c r="H90">
         <v>2152636955601.996</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90">
         <v>25685010192018.05</v>
       </c>
-      <c r="J90" t="n">
+      <c r="J90">
         <v>2430548737957.025</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K90">
         <v>11154119805058.46</v>
       </c>
-      <c r="L90" t="n">
+      <c r="L90">
         <v>2346802618648.897</v>
       </c>
-      <c r="M90" t="n">
+      <c r="M90">
         <v>11251332216077.3</v>
       </c>
-      <c r="N90" t="n">
+      <c r="N90">
         <v>571879232750.2992</v>
       </c>
-      <c r="O90" t="n">
+      <c r="O90">
         <v>7818993017718.639</v>
       </c>
-      <c r="P90" t="n">
+      <c r="P90">
         <v>7798761318790.222</v>
       </c>
-      <c r="Q90" t="n">
+      <c r="Q90">
         <v>78400599818.55766</v>
       </c>
-      <c r="R90" t="n">
+      <c r="R90">
         <v>654782018047.4934</v>
       </c>
-      <c r="S90" t="n">
+      <c r="S90">
         <v>74861945011.90091</v>
       </c>
-      <c r="T90" t="n">
+      <c r="T90">
         <v>728771545871.8507</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
+    <row r="91" spans="1:20">
+      <c r="A91" s="2">
         <v>44377</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>557531834727.9817</v>
       </c>
-      <c r="C91" t="n">
+      <c r="C91">
         <v>4124376843248.763</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>552897832919.9827</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>4174553018360.75</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>2160226669658.335</v>
       </c>
-      <c r="G91" t="n">
+      <c r="G91">
         <v>26566581848584.12</v>
       </c>
-      <c r="H91" t="n">
+      <c r="H91">
         <v>2161781643497.629</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91">
         <v>26354186198570.19</v>
       </c>
-      <c r="J91" t="n">
+      <c r="J91">
         <v>2691306959920.736</v>
       </c>
-      <c r="K91" t="n">
+      <c r="K91">
         <v>12370220999941.18</v>
       </c>
-      <c r="L91" t="n">
+      <c r="L91">
         <v>2820714499900.977</v>
       </c>
-      <c r="M91" t="n">
+      <c r="M91">
         <v>12245258823329.43</v>
       </c>
-      <c r="N91" t="n">
+      <c r="N91">
         <v>559734891947.8518</v>
       </c>
-      <c r="O91" t="n">
+      <c r="O91">
         <v>7544343350508.612</v>
       </c>
-      <c r="P91" t="n">
+      <c r="P91">
         <v>7954646587414.847</v>
       </c>
-      <c r="Q91" t="n">
+      <c r="Q91">
         <v>82535157233.32138</v>
       </c>
-      <c r="R91" t="n">
+      <c r="R91">
         <v>748424265318.4475</v>
       </c>
-      <c r="S91" t="n">
+      <c r="S91">
         <v>82043030916.06514</v>
       </c>
-      <c r="T91" t="n">
+      <c r="T91">
         <v>745046764496.0968</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
+    <row r="92" spans="1:20">
+      <c r="A92" s="2">
         <v>44469</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>590279565152.3756</v>
       </c>
-      <c r="C92" t="n">
+      <c r="C92">
         <v>4264516714610.403</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>609225031830.5579</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>4228282464600.52</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>2153206774403.947</v>
       </c>
-      <c r="G92" t="n">
+      <c r="G92">
         <v>27115933807077.7</v>
       </c>
-      <c r="H92" t="n">
+      <c r="H92">
         <v>2177650765011.222</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92">
         <v>27159076834820.47</v>
       </c>
-      <c r="J92" t="n">
+      <c r="J92">
         <v>2988487320739.498</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92">
         <v>12407696153560.16</v>
       </c>
-      <c r="L92" t="n">
+      <c r="L92">
         <v>3088268966177.471</v>
       </c>
-      <c r="M92" t="n">
+      <c r="M92">
         <v>12192524715786.72</v>
       </c>
-      <c r="N92" t="n">
+      <c r="N92">
         <v>506997510746.2547</v>
       </c>
-      <c r="O92" t="n">
+      <c r="O92">
         <v>11914555794994.48</v>
       </c>
-      <c r="P92" t="n">
+      <c r="P92">
         <v>12644418740156.67</v>
       </c>
-      <c r="Q92" t="n">
+      <c r="Q92">
         <v>87521289717.41023</v>
       </c>
-      <c r="R92" t="n">
+      <c r="R92">
         <v>817243248411.4197</v>
       </c>
-      <c r="S92" t="n">
+      <c r="S92">
         <v>89416911208.94757</v>
       </c>
-      <c r="T92" t="n">
+      <c r="T92">
         <v>797956143933.6306</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
+    <row r="93" spans="1:20">
+      <c r="A93" s="2">
         <v>44561</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>646112852361.1969</v>
       </c>
-      <c r="C93" t="n">
+      <c r="C93">
         <v>4721260507470.119</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>642689232894.505</v>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>4331436239003.166</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>2187949003090.902</v>
       </c>
-      <c r="G93" t="n">
+      <c r="G93">
         <v>27333775020412.12</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H93">
         <v>2213893666763.343</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I93">
         <v>27562063039155.93</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J93">
         <v>3002900532752.283</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93">
         <v>12995023999253.81</v>
       </c>
-      <c r="L93" t="n">
+      <c r="L93">
         <v>2816896607968.36</v>
       </c>
-      <c r="M93" t="n">
+      <c r="M93">
         <v>13254220671636.78</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N93">
         <v>508089211890.2893</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O93">
         <v>9519762866594.641</v>
       </c>
-      <c r="P93" t="n">
+      <c r="P93">
         <v>8196374750506.882</v>
       </c>
-      <c r="Q93" t="n">
+      <c r="Q93">
         <v>90369276897.91325</v>
       </c>
-      <c r="R93" t="n">
+      <c r="R93">
         <v>875656437560.2502</v>
       </c>
-      <c r="S93" t="n">
+      <c r="S93">
         <v>93128383786.09232</v>
       </c>
-      <c r="T93" t="n">
+      <c r="T93">
         <v>826475433877.2783</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
+    <row r="94" spans="1:20">
+      <c r="A94" s="2">
         <v>44651</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>679335825363.4681</v>
       </c>
-      <c r="C94" t="n">
+      <c r="C94">
         <v>3899806582150.777</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D94">
         <v>665649593216.4703</v>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>4274422037009.355</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>2266296815183.478</v>
       </c>
-      <c r="G94" t="n">
+      <c r="G94">
         <v>28281842620245.77</v>
       </c>
-      <c r="H94" t="n">
+      <c r="H94">
         <v>2212917088235.767</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94">
         <v>28216046014391.94</v>
       </c>
-      <c r="J94" t="n">
+      <c r="J94">
         <v>2980238343991.764</v>
       </c>
-      <c r="K94" t="n">
+      <c r="K94">
         <v>11327688038185.95</v>
       </c>
-      <c r="L94" t="n">
+      <c r="L94">
         <v>2903720586431.87</v>
       </c>
-      <c r="M94" t="n">
+      <c r="M94">
         <v>11533297192245.64</v>
       </c>
-      <c r="N94" t="n">
+      <c r="N94">
         <v>464467647971.9963</v>
       </c>
-      <c r="O94" t="n">
+      <c r="O94">
         <v>8230954489659.232</v>
       </c>
-      <c r="P94" t="n">
+      <c r="P94">
         <v>8468287707452.813</v>
       </c>
-      <c r="Q94" t="n">
+      <c r="Q94">
         <v>99406721598.36812</v>
       </c>
-      <c r="R94" t="n">
+      <c r="R94">
         <v>733129053037.9877</v>
       </c>
-      <c r="S94" t="n">
+      <c r="S94">
         <v>95109435220.58728</v>
       </c>
-      <c r="T94" t="n">
+      <c r="T94">
         <v>805629936681.0488</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
+    <row r="95" spans="1:20">
+      <c r="A95" s="2">
         <v>44742</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>650507160718.5876</v>
       </c>
-      <c r="C95" t="n">
+      <c r="C95">
         <v>4189324836280.844</v>
       </c>
-      <c r="D95" t="n">
+      <c r="D95">
         <v>647877377922.3932</v>
       </c>
-      <c r="E95" t="n">
+      <c r="E95">
         <v>4247150546225.57</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>2226409028294.669</v>
       </c>
-      <c r="G95" t="n">
+      <c r="G95">
         <v>28901333701953.41</v>
       </c>
-      <c r="H95" t="n">
+      <c r="H95">
         <v>2227683156362.28</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95">
         <v>28660477342839.93</v>
       </c>
-      <c r="J95" t="n">
+      <c r="J95">
         <v>2680962157189.475</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K95">
         <v>11880726105452.44</v>
       </c>
-      <c r="L95" t="n">
+      <c r="L95">
         <v>2868240232121.247</v>
       </c>
-      <c r="M95" t="n">
+      <c r="M95">
         <v>11537770924878.39</v>
       </c>
-      <c r="N95" t="n">
+      <c r="N95">
         <v>407791686182.9131</v>
       </c>
-      <c r="O95" t="n">
+      <c r="O95">
         <v>7831093879112.714</v>
       </c>
-      <c r="P95" t="n">
+      <c r="P95">
         <v>8246897953699.528</v>
       </c>
-      <c r="Q95" t="n">
+      <c r="Q95">
         <v>102738834911.229</v>
       </c>
-      <c r="R95" t="n">
+      <c r="R95">
         <v>847235242149.021</v>
       </c>
-      <c r="S95" t="n">
+      <c r="S95">
         <v>101944970721.3489</v>
       </c>
-      <c r="T95" t="n">
+      <c r="T95">
         <v>838896164859.8868</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
+    <row r="96" spans="1:20">
+      <c r="A96" s="2">
         <v>44834</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>639327222116.7777</v>
       </c>
-      <c r="C96" t="n">
+      <c r="C96">
         <v>4397487016723.344</v>
       </c>
-      <c r="D96" t="n">
+      <c r="D96">
         <v>661620982413.2593</v>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>4363908220221.786</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>2266788882932.173</v>
       </c>
-      <c r="G96" t="n">
+      <c r="G96">
         <v>29385148649144.95</v>
       </c>
-      <c r="H96" t="n">
+      <c r="H96">
         <v>2295813375004.479</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96">
         <v>29472611239373.77</v>
       </c>
-      <c r="J96" t="n">
+      <c r="J96">
         <v>2948122678757.646</v>
       </c>
-      <c r="K96" t="n">
+      <c r="K96">
         <v>10594169482114.78</v>
       </c>
-      <c r="L96" t="n">
+      <c r="L96">
         <v>3063642990640.002</v>
       </c>
-      <c r="M96" t="n">
+      <c r="M96">
         <v>10476644141444.3</v>
       </c>
-      <c r="N96" t="n">
+      <c r="N96">
         <v>407128166638.8411</v>
       </c>
-      <c r="O96" t="n">
+      <c r="O96">
         <v>8316418430038.632</v>
       </c>
-      <c r="P96" t="n">
+      <c r="P96">
         <v>9065743444745.492</v>
       </c>
-      <c r="Q96" t="n">
+      <c r="Q96">
         <v>95824856509.28802</v>
       </c>
-      <c r="R96" t="n">
+      <c r="R96">
         <v>927714896994.7761</v>
       </c>
-      <c r="S96" t="n">
+      <c r="S96">
         <v>98054162817.57098</v>
       </c>
-      <c r="T96" t="n">
+      <c r="T96">
         <v>913573609052.0237</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
+    <row r="97" spans="1:20">
+      <c r="A97" s="2">
         <v>44926</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>669586841997.323</v>
       </c>
-      <c r="C97" t="n">
+      <c r="C97">
         <v>4768518006290.657</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D97">
         <v>665054709106.0607</v>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>4361747424836.008</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>2319095086763.771</v>
       </c>
-      <c r="G97" t="n">
+      <c r="G97">
         <v>29806199838828.43</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H97">
         <v>2344226569378.426</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97">
         <v>30084587256572.11</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J97">
         <v>3016911460014.099</v>
       </c>
-      <c r="K97" t="n">
+      <c r="K97">
         <v>10976204958796.87</v>
       </c>
-      <c r="L97" t="n">
+      <c r="L97">
         <v>2754007308489.322</v>
       </c>
-      <c r="M97" t="n">
+      <c r="M97">
         <v>11248957064239.15</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N97">
         <v>374190214312.9719</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O97">
         <v>7026969859660.892</v>
       </c>
-      <c r="P97" t="n">
+      <c r="P97">
         <v>5426349834368.002</v>
       </c>
-      <c r="Q97" t="n">
+      <c r="Q97">
         <v>91846706197.68404</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R97">
         <v>893555833978.8331</v>
       </c>
-      <c r="S97" t="n">
+      <c r="S97">
         <v>95310030683.07164</v>
       </c>
-      <c r="T97" t="n">
+      <c r="T97">
         <v>846206103534.4678</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
+    <row r="98" spans="1:20">
+      <c r="A98" s="2">
         <v>45016</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>699296890146.6774</v>
       </c>
-      <c r="C98" t="n">
+      <c r="C98">
         <v>4063255246931.068</v>
       </c>
-      <c r="D98" t="n">
+      <c r="D98">
         <v>681280595309.5016</v>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>4442004699846.762</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>2417238881052.903</v>
       </c>
-      <c r="G98" t="n">
+      <c r="G98">
         <v>31331751247210.73</v>
       </c>
-      <c r="H98" t="n">
+      <c r="H98">
         <v>2360127563730.712</v>
       </c>
-      <c r="I98" t="n">
+      <c r="I98">
         <v>31192718635941.01</v>
       </c>
-      <c r="J98" t="n">
+      <c r="J98">
         <v>2748165983063.038</v>
       </c>
-      <c r="K98" t="n">
+      <c r="K98">
         <v>11797134733581.34</v>
       </c>
-      <c r="L98" t="n">
+      <c r="L98">
         <v>2676979681526.917</v>
       </c>
-      <c r="M98" t="n">
+      <c r="M98">
         <v>12100228073450.18</v>
       </c>
-      <c r="N98" t="n">
+      <c r="N98">
         <v>344172826861.5703</v>
       </c>
-      <c r="O98" t="n">
+      <c r="O98">
         <v>7224093455453.676</v>
       </c>
-      <c r="P98" t="n">
+      <c r="P98">
         <v>7717820360193.449</v>
       </c>
-      <c r="Q98" t="n">
+      <c r="Q98">
         <v>100499526712.5604</v>
       </c>
-      <c r="R98" t="n">
+      <c r="R98">
         <v>781835315335.3807</v>
       </c>
-      <c r="S98" t="n">
+      <c r="S98">
         <v>95524671409.20236</v>
       </c>
-      <c r="T98" t="n">
+      <c r="T98">
         <v>852468780575.9479</v>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
+    <row r="99" spans="1:20">
+      <c r="A99" s="2">
         <v>45107</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>688231897343.828</v>
       </c>
-      <c r="C99" t="n">
+      <c r="C99">
         <v>4424885846254.873</v>
       </c>
-      <c r="D99" t="n">
+      <c r="D99">
         <v>687695386971.66</v>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>4491417784994.333</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>2450345203852.955</v>
       </c>
-      <c r="G99" t="n">
+      <c r="G99">
         <v>32262949180116.05</v>
       </c>
-      <c r="H99" t="n">
+      <c r="H99">
         <v>2451133001160.736</v>
       </c>
-      <c r="I99" t="n">
+      <c r="I99">
         <v>31994719083065.22</v>
       </c>
-      <c r="J99" t="n">
+      <c r="J99">
         <v>3105020784768.853</v>
       </c>
-      <c r="K99" t="n">
+      <c r="K99">
         <v>11650184311323.38</v>
       </c>
-      <c r="L99" t="n">
+      <c r="L99">
         <v>3351315964530.233</v>
       </c>
-      <c r="M99" t="n">
+      <c r="M99">
         <v>11084347176478.74</v>
       </c>
-      <c r="N99" t="n">
+      <c r="N99">
         <v>389065725629.7455</v>
       </c>
-      <c r="O99" t="n">
+      <c r="O99">
         <v>8322848967971.639</v>
       </c>
-      <c r="P99" t="n">
+      <c r="P99">
         <v>8735785460252.732</v>
       </c>
-      <c r="Q99" t="n">
+      <c r="Q99">
         <v>89441439607.91837</v>
       </c>
-      <c r="R99" t="n">
+      <c r="R99">
         <v>848133227470.1621</v>
       </c>
-      <c r="S99" t="n">
+      <c r="S99">
         <v>88316374124.32819</v>
       </c>
-      <c r="T99" t="n">
+      <c r="T99">
         <v>834738252635.1399</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
+    <row r="100" spans="1:20">
+      <c r="A100" s="2">
         <v>45199</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>672798805709.2651</v>
       </c>
-      <c r="C100" t="n">
+      <c r="C100">
         <v>4582270334306.942</v>
       </c>
-      <c r="D100" t="n">
+      <c r="D100">
         <v>698484608084.5988</v>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>4551825159530.381</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>2474601319709.541</v>
       </c>
-      <c r="G100" t="n">
+      <c r="G100">
         <v>32729385144494.54</v>
       </c>
-      <c r="H100" t="n">
+      <c r="H100">
         <v>2508410607359.57</v>
       </c>
-      <c r="I100" t="n">
+      <c r="I100">
         <v>32862150367949.65</v>
       </c>
-      <c r="J100" t="n">
+      <c r="J100">
         <v>3252497773713.606</v>
       </c>
-      <c r="K100" t="n">
+      <c r="K100">
         <v>11183878540931.9</v>
       </c>
-      <c r="L100" t="n">
+      <c r="L100">
         <v>3381787687690.481</v>
       </c>
-      <c r="M100" t="n">
+      <c r="M100">
         <v>11174596065670.9</v>
       </c>
-      <c r="N100" t="n">
+      <c r="N100">
         <v>530939375172.2943</v>
       </c>
-      <c r="O100" t="n">
+      <c r="O100">
         <v>7141226567730.516</v>
       </c>
-      <c r="P100" t="n">
+      <c r="P100">
         <v>7908466897891.621</v>
       </c>
-      <c r="Q100" t="n">
+      <c r="Q100">
         <v>90319715042.88055</v>
       </c>
-      <c r="R100" t="n">
+      <c r="R100">
         <v>875249188066.3146</v>
       </c>
-      <c r="S100" t="n">
+      <c r="S100">
         <v>92844493636.99806</v>
       </c>
-      <c r="T100" t="n">
+      <c r="T100">
         <v>866326700458.8967</v>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
+    <row r="101" spans="1:20">
+      <c r="A101" s="2">
         <v>45291</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>712741812154.2268</v>
       </c>
-      <c r="C101" t="n">
+      <c r="C101">
         <v>4991918373570.701</v>
       </c>
-      <c r="D101" t="n">
+      <c r="D101">
         <v>707015042099.1335</v>
       </c>
-      <c r="E101" t="n">
+      <c r="E101">
         <v>4568756642178.866</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>2556213267308.208</v>
       </c>
-      <c r="G101" t="n">
+      <c r="G101">
         <v>33201294172096.38</v>
       </c>
-      <c r="H101" t="n">
+      <c r="H101">
         <v>2580739359473.594</v>
       </c>
-      <c r="I101" t="n">
+      <c r="I101">
         <v>33531950803902.12</v>
       </c>
-      <c r="J101" t="n">
+      <c r="J101">
         <v>3714346655294.693</v>
       </c>
-      <c r="K101" t="n">
+      <c r="K101">
         <v>10803856319309.55</v>
       </c>
-      <c r="L101" t="n">
+      <c r="L101">
         <v>3374123933628.983</v>
       </c>
-      <c r="M101" t="n">
+      <c r="M101">
         <v>11085757227060.99</v>
       </c>
-      <c r="N101" t="n">
+      <c r="N101">
         <v>536254215960.9401</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O101">
         <v>6926020010053.418</v>
       </c>
-      <c r="P101" t="n">
+      <c r="P101">
         <v>5047064890102.825</v>
       </c>
-      <c r="Q101" t="n">
+      <c r="Q101">
         <v>89634212405.24188</v>
       </c>
-      <c r="R101" t="n">
+      <c r="R101">
         <v>879349361892.1304</v>
       </c>
-      <c r="S101" t="n">
+      <c r="S101">
         <v>93775726063.28596</v>
       </c>
-      <c r="T101" t="n">
+      <c r="T101">
         <v>833569546545.6199</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
+    <row r="102" spans="1:20">
+      <c r="A102" s="2">
         <v>45382</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>738075020110.1312</v>
       </c>
-      <c r="C102" t="n">
+      <c r="C102">
         <v>4233564551709.118</v>
       </c>
-      <c r="D102" t="n">
+      <c r="D102">
         <v>715679294632.9504</v>
       </c>
-      <c r="E102" t="n">
+      <c r="E102">
         <v>4616455970162.326</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>2638231416428.826</v>
       </c>
-      <c r="G102" t="n">
+      <c r="G102">
         <v>34345239033315.63</v>
       </c>
-      <c r="H102" t="n">
+      <c r="H102">
         <v>2577725978624.497</v>
       </c>
-      <c r="I102" t="n">
+      <c r="I102">
         <v>34133681264636.94</v>
       </c>
-      <c r="J102" t="n">
+      <c r="J102">
         <v>3939000258045.221</v>
       </c>
-      <c r="K102" t="n">
+      <c r="K102">
         <v>10690022361343.29</v>
       </c>
-      <c r="L102" t="n">
+      <c r="L102">
         <v>3873379801671.581</v>
       </c>
-      <c r="M102" t="n">
+      <c r="M102">
         <v>11094129006291.71</v>
       </c>
-      <c r="N102" t="n">
+      <c r="N102">
         <v>746678633361.186</v>
       </c>
-      <c r="O102" t="n">
+      <c r="O102">
         <v>7157580622245.104</v>
       </c>
-      <c r="P102" t="n">
+      <c r="P102">
         <v>7920267419565.078</v>
       </c>
-      <c r="Q102" t="n">
+      <c r="Q102">
         <v>101769703150.2202</v>
       </c>
-      <c r="R102" t="n">
+      <c r="R102">
         <v>807130254716.1978</v>
       </c>
-      <c r="S102" t="n">
+      <c r="S102">
         <v>96115617591.30914</v>
       </c>
-      <c r="T102" t="n">
+      <c r="T102">
         <v>876041040807.8352</v>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="n">
+    <row r="103" spans="1:20">
+      <c r="A103" s="2">
         <v>45473</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>725908076367.8806</v>
       </c>
-      <c r="C103" t="n">
+      <c r="C103">
         <v>4587254862127.495</v>
       </c>
-      <c r="D103" t="n">
+      <c r="D103">
         <v>727524183732.1504</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E103">
         <v>4662766374774.279</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>2682476190173.511</v>
       </c>
-      <c r="G103" t="n">
+      <c r="G103">
         <v>35020577529146.96</v>
       </c>
-      <c r="H103" t="n">
+      <c r="H103">
         <v>2682355241061.75</v>
       </c>
-      <c r="I103" t="n">
+      <c r="I103">
         <v>34725076837638.57</v>
       </c>
-      <c r="J103" t="n">
+      <c r="J103">
         <v>4431800409337.394</v>
       </c>
-      <c r="K103" t="n">
+      <c r="K103">
         <v>10235224998813.85</v>
       </c>
-      <c r="L103" t="n">
+      <c r="L103">
         <v>4735836798930.247</v>
       </c>
-      <c r="M103" t="n">
+      <c r="M103">
         <v>9444786367881.941</v>
       </c>
-      <c r="N103" t="n">
+      <c r="N103">
         <v>801153638645.6022</v>
       </c>
-      <c r="O103" t="n">
+      <c r="O103">
         <v>6821744337150.074</v>
       </c>
-      <c r="P103" t="n">
+      <c r="P103">
         <v>7227297110486.617</v>
       </c>
-      <c r="Q103" t="n">
+      <c r="Q103">
         <v>95976691588.17166</v>
       </c>
-      <c r="R103" t="n">
+      <c r="R103">
         <v>912714214551.7704</v>
       </c>
-      <c r="S103" t="n">
+      <c r="S103">
         <v>94512886894.5394</v>
       </c>
-      <c r="T103" t="n">
+      <c r="T103">
         <v>894144421747.9742</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="n">
+    <row r="104" spans="1:20">
+      <c r="A104" s="2">
         <v>45565</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>707577896957.707</v>
       </c>
-      <c r="C104" t="n">
+      <c r="C104">
         <v>4740701220075.682</v>
       </c>
-      <c r="D104" t="n">
+      <c r="D104">
         <v>736697489740.3156</v>
       </c>
-      <c r="E104" t="n">
+      <c r="E104">
         <v>4713383980953.432</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>2643557985475.203</v>
       </c>
-      <c r="G104" t="n">
+      <c r="G104">
         <v>35212098994682.2</v>
       </c>
-      <c r="H104" t="n">
+      <c r="H104">
         <v>2681901235180.667</v>
       </c>
-      <c r="I104" t="n">
+      <c r="I104">
         <v>35391009504654.87</v>
       </c>
-      <c r="J104" t="n">
+      <c r="J104">
         <v>4697766954823.038</v>
       </c>
-      <c r="K104" t="n">
+      <c r="K104">
         <v>11701143894573.58</v>
       </c>
-      <c r="L104" t="n">
+      <c r="L104">
         <v>4839549588432.961</v>
       </c>
-      <c r="M104" t="n">
+      <c r="M104">
         <v>11804665448145.47</v>
       </c>
-      <c r="N104" t="n">
+      <c r="N104">
         <v>867726732817.8638</v>
       </c>
-      <c r="O104" t="n">
+      <c r="O104">
         <v>5997316599849.313</v>
       </c>
-      <c r="P104" t="n">
+      <c r="P104">
         <v>6782347113813.592</v>
       </c>
-      <c r="Q104" t="n">
+      <c r="Q104">
         <v>82668053963.34303</v>
       </c>
-      <c r="R104" t="n">
+      <c r="R104">
         <v>907940505622.0802</v>
       </c>
-      <c r="S104" t="n">
+      <c r="S104">
         <v>85562121868.28763</v>
       </c>
-      <c r="T104" t="n">
+      <c r="T104">
         <v>904350562415.7522</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="n">
+    <row r="105" spans="1:20">
+      <c r="A105" s="2">
         <v>45657</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>758906201548.8108</v>
       </c>
-      <c r="C105" t="n">
+      <c r="C105">
         <v>5209408278853.68</v>
       </c>
-      <c r="D105" t="n">
+      <c r="D105">
         <v>751801486555.6526</v>
       </c>
-      <c r="E105" t="n">
+      <c r="E105">
         <v>4769792021565.23</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>2706754026882.17</v>
       </c>
-      <c r="G105" t="n">
+      <c r="G105">
         <v>35659596774743.47</v>
       </c>
-      <c r="H105" t="n">
+      <c r="H105">
         <v>2730797760783.432</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I105">
         <v>36043172685982.61</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J105">
         <v>4335416937646.872</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K105">
         <v>11920857666737.83</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L105">
         <v>3918310939252.205</v>
       </c>
-      <c r="M105" t="n">
+      <c r="M105">
         <v>12207671063109.21</v>
       </c>
-      <c r="N105" t="n">
+      <c r="N105">
         <v>663139095475.4001</v>
       </c>
-      <c r="O105" t="n">
+      <c r="O105">
         <v>15514898223104.44</v>
       </c>
-      <c r="P105" t="n">
+      <c r="P105">
         <v>13357502036130.2</v>
       </c>
-      <c r="Q105" t="n">
+      <c r="Q105">
         <v>90086231372.27582</v>
       </c>
-      <c r="R105" t="n">
+      <c r="R105">
         <v>960610696059.8486</v>
       </c>
-      <c r="S105" t="n">
+      <c r="S105">
         <v>94885727829.85899</v>
       </c>
-      <c r="T105" t="n">
+      <c r="T105">
         <v>916319128006.8829</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="n">
+    <row r="106" spans="1:20">
+      <c r="A106" s="2">
         <v>45747</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>786244358686.6851</v>
       </c>
-      <c r="C106" t="n">
+      <c r="C106">
         <v>4433085622689.654</v>
       </c>
-      <c r="D106" t="n">
+      <c r="D106">
         <v>759514370306.9235</v>
       </c>
-      <c r="E106" t="n">
+      <c r="E106">
         <v>4819947153622.317</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>2849807414922.103</v>
       </c>
-      <c r="G106" t="n">
+      <c r="G106">
         <v>36945860400849.98</v>
       </c>
-      <c r="H106" t="n">
+      <c r="H106">
         <v>2786026073849.99</v>
       </c>
-      <c r="I106" t="n">
+      <c r="I106">
         <v>36661681821305.99</v>
       </c>
-      <c r="J106" t="n">
+      <c r="J106">
         <v>4085134067981.061</v>
       </c>
-      <c r="K106" t="n">
+      <c r="K106">
         <v>12043363870128.58</v>
       </c>
-      <c r="L106" t="n">
+      <c r="L106">
         <v>4026709334857.141</v>
       </c>
-      <c r="M106" t="n">
+      <c r="M106">
         <v>12548771403681.29</v>
       </c>
-      <c r="N106" t="n">
+      <c r="N106">
         <v>606925510157.277</v>
       </c>
-      <c r="O106" t="n">
+      <c r="O106">
         <v>11882932218015.07</v>
       </c>
-      <c r="P106" t="n">
+      <c r="P106">
         <v>12922316996869.06</v>
       </c>
-      <c r="Q106" t="n">
+      <c r="Q106">
         <v>98853679522.802</v>
       </c>
-      <c r="R106" t="n">
+      <c r="R106">
         <v>865313537868.6857</v>
       </c>
-      <c r="S106" t="n">
+      <c r="S106">
         <v>92533710127.1328</v>
       </c>
-      <c r="T106" t="n">
+      <c r="T106">
         <v>932649280297.3582</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
+    <mergeCell ref="L1:M1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="D1:E1"/>
     <mergeCell ref="S1:T1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>